--- a/Versão5/PRO/Ontologia_Agentes.xlsx
+++ b/Versão5/PRO/Ontologia_Agentes.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AGIR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77522B81-AACC-48EE-B6BD-4C5551964E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F1C917-98E1-4B61-9BC0-2A094EC4056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="197">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -388,18 +388,6 @@
     <t>Declara a um Agente Artificial</t>
   </si>
   <si>
-    <t>Declares to a Human Agent</t>
-  </si>
-  <si>
-    <t>Declares to an Artificial Agent</t>
-  </si>
-  <si>
-    <t>Declara a un agente humano</t>
-  </si>
-  <si>
-    <t>Declara a un agente artificial</t>
-  </si>
-  <si>
     <t>é.agente.de</t>
   </si>
   <si>
@@ -481,9 +469,6 @@
     <t>Artificiais</t>
   </si>
   <si>
-    <t>"Verificar requisitos"</t>
-  </si>
-  <si>
     <t>"Distribuir luminárias"</t>
   </si>
   <si>
@@ -499,9 +484,6 @@
     <t>Declara a linguagem Gherkin, para processos BDD (Behaviour-Driven Development).</t>
   </si>
   <si>
-    <t>Declares the Gherkin language, for BDD (Behaviour-Driven Development) processes.</t>
-  </si>
-  <si>
     <t>Linguagens</t>
   </si>
   <si>
@@ -529,12 +511,6 @@
     <t>Conceitos</t>
   </si>
   <si>
-    <t>Agênticos</t>
-  </si>
-  <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>agente.de</t>
   </si>
   <si>
@@ -544,30 +520,12 @@
     <t>Projeto</t>
   </si>
   <si>
-    <t>Agente</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>Inteligência</t>
-  </si>
-  <si>
-    <t>Define um agente utilizado no Projeto.</t>
-  </si>
-  <si>
     <t>Linguagem</t>
   </si>
   <si>
     <t>Sintaxe</t>
   </si>
   <si>
-    <t>Define uma linguagem utilizada para automatizar tarefas do projeto.</t>
-  </si>
-  <si>
-    <t>Define uma sintaxe utilizada para automatizar tarefas do projeto.</t>
-  </si>
-  <si>
     <t>Projeto_A</t>
   </si>
   <si>
@@ -580,16 +538,130 @@
     <t>"Projeto de arquitetura"</t>
   </si>
   <si>
-    <t>"Escola"</t>
-  </si>
-  <si>
     <t>etapa</t>
   </si>
   <si>
     <t>"Estudo preliminar"</t>
   </si>
   <si>
-    <t>API.Agentes</t>
+    <t>"Verificar requisitos atendidos"</t>
+  </si>
+  <si>
+    <t>0 Val</t>
+  </si>
+  <si>
+    <t>categoria.revit</t>
+  </si>
+  <si>
+    <t>"[ OST_ProjectInformation : OST_ProjectBasePoint : OST_SitePoint : OST_SharedBasePoint ]"</t>
+  </si>
+  <si>
+    <t>classe.ifc</t>
+  </si>
+  <si>
+    <t>"[ IfcProject : IfcText : IfcLabel ]"</t>
+  </si>
+  <si>
+    <t>código.abnt</t>
+  </si>
+  <si>
+    <t>"[ 4U.70.10.02 ]"</t>
+  </si>
+  <si>
+    <t>"Faculdade"</t>
+  </si>
+  <si>
+    <t>De.Inteligência.Projetual</t>
+  </si>
+  <si>
+    <t>Computacionais</t>
+  </si>
+  <si>
+    <t>Agêntica.Artificial</t>
+  </si>
+  <si>
+    <t>Orquestações</t>
+  </si>
+  <si>
+    <t>Agentes.Humanos</t>
+  </si>
+  <si>
+    <t>Agentes.Artificiais</t>
+  </si>
+  <si>
+    <t>Projetista</t>
+  </si>
+  <si>
+    <t>Agente.IA</t>
+  </si>
+  <si>
+    <t>Sintática</t>
+  </si>
+  <si>
+    <t>Semântica</t>
+  </si>
+  <si>
+    <t>Inteligente</t>
+  </si>
+  <si>
+    <t>Declara um projetista humano que trabalha no projeto.</t>
+  </si>
+  <si>
+    <t>Declara um agente artificial utilizado para o projeto.</t>
+  </si>
+  <si>
+    <t>Semântico</t>
+  </si>
+  <si>
+    <t>Declara uma semântica específca utilizada para dar significado aos elementos do projeto.</t>
+  </si>
+  <si>
+    <t>HU-01</t>
+  </si>
+  <si>
+    <t>"José"</t>
+  </si>
+  <si>
+    <t>"Arquiteto do projeto"</t>
+  </si>
+  <si>
+    <t>HU-02</t>
+  </si>
+  <si>
+    <t>"João"</t>
+  </si>
+  <si>
+    <t>"Engenheiro calculista do projeto"</t>
+  </si>
+  <si>
+    <t>"[ 1D.21.11 ]"</t>
+  </si>
+  <si>
+    <t>"[ 1D.21.31.14 ]"</t>
+  </si>
+  <si>
+    <t>Agêntica.Natural</t>
+  </si>
+  <si>
+    <t>Calculista</t>
+  </si>
+  <si>
+    <t>Declara um idioma natural utilizado em tarefas do projeto.</t>
+  </si>
+  <si>
+    <t>Declara uma linguagem computacional utilizada para automatizar tarefas do projeto.</t>
+  </si>
+  <si>
+    <t>Declara uma sintaxe artificial utilizada para automatizar tarefas do projeto.</t>
+  </si>
+  <si>
+    <t>Declara um calculista humano que trabalha no projeto.</t>
+  </si>
+  <si>
+    <t>Declara uma semântica computacional utilizada (ex. KML, OKF, etc).</t>
+  </si>
+  <si>
+    <t>Declara uma sintaxe computacional utilizada (ex. Manchester, TTL).</t>
   </si>
 </sst>
 </file>
@@ -895,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1067,21 +1139,56 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="16">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1103,11 +1210,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1203,136 +1312,6 @@
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
   </dxfs>
@@ -1941,7 +1920,7 @@
       </c>
       <c r="B18" s="20">
         <f ca="1">NOW()</f>
-        <v>46244.519561111112</v>
+        <v>46248.624910763887</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>87</v>
@@ -2047,30 +2026,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA7"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" style="13" customWidth="1"/>
     <col min="7" max="11" width="7.7109375" style="13" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" style="13" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="12" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="2" customWidth="1"/>
     <col min="16" max="16" width="37.5703125" style="13" customWidth="1"/>
     <col min="17" max="17" width="42.85546875" style="13" customWidth="1"/>
     <col min="18" max="18" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8.5703125" style="13" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="6.5703125" style="32" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.85546875" style="32" customWidth="1"/>
+    <col min="25" max="25" width="6.5703125" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.140625" style="31" customWidth="1"/>
     <col min="27" max="27" width="45.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="28" max="16384" width="9.140625" style="2"/>
   </cols>
@@ -2163,16 +2143,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="F2" s="35" t="s">
         <v>97</v>
@@ -2194,15 +2174,15 @@
       </c>
       <c r="L2" s="36" t="str">
         <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
-        <v>Agênticos</v>
+        <v>De.Inteligência.Projetual</v>
       </c>
       <c r="M2" s="36" t="str">
         <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
-        <v>Agentes</v>
+        <v>Orquestações</v>
       </c>
       <c r="N2" s="36" t="str">
         <f t="shared" ref="N2:O2" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Humanos</v>
+        <v>Agentes Humanos</v>
       </c>
       <c r="O2" s="36" t="str">
         <f t="shared" si="2"/>
@@ -2211,42 +2191,44 @@
       <c r="P2" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="Q2" s="37" t="s">
-        <v>107</v>
+      <c r="Q2" s="37" t="str">
+        <f t="shared" ref="Q2:Q13" si="3">_xlfn.TRANSLATE(P2,"pt","es")</f>
+        <v>Declara a un agente humano</v>
       </c>
       <c r="R2" s="38" t="s">
         <v>10</v>
       </c>
       <c r="S2" s="38" t="str">
-        <f t="shared" ref="S2:U2" si="3">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Agênticos</v>
+        <f t="shared" ref="S2:U2" si="4">SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Inteligência Projetual</v>
       </c>
       <c r="T2" s="38" t="str">
-        <f t="shared" si="3"/>
-        <v>Agentes</v>
+        <f t="shared" si="4"/>
+        <v>Orquestações</v>
       </c>
       <c r="U2" s="38" t="str">
-        <f t="shared" si="3"/>
-        <v>Humanos</v>
+        <f t="shared" si="4"/>
+        <v>Agentes Humanos</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="W2" s="52" t="str">
-        <f t="shared" ref="W2:W5" si="4">CONCATENATE("Key-AGEN-",A2)</f>
+        <f t="shared" ref="W2:W13" si="5">CONCATENATE("Key-AGEN-",A2)</f>
         <v>Key-AGEN-2</v>
       </c>
       <c r="X2" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Y2" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA2" s="37" t="s">
-        <v>105</v>
+        <v>10</v>
+      </c>
+      <c r="AA2" s="37" t="str">
+        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Declares to a Human Agent</v>
       </c>
     </row>
     <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2254,16 +2236,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D3" s="34" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="E3" s="34" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="F3" s="35" t="s">
         <v>101</v>
@@ -2284,60 +2266,62 @@
         <v>10</v>
       </c>
       <c r="L3" s="36" t="str">
-        <f t="shared" ref="L3:M3" si="5">CONCATENATE("", C3)</f>
-        <v>Agênticos</v>
+        <f t="shared" ref="L3:M5" si="6">CONCATENATE("", C3)</f>
+        <v>De.Inteligência.Projetual</v>
       </c>
       <c r="M3" s="36" t="str">
-        <f t="shared" si="5"/>
-        <v>Agentes</v>
+        <f t="shared" si="6"/>
+        <v>Orquestações</v>
       </c>
       <c r="N3" s="36" t="str">
-        <f t="shared" ref="N3:O3" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
-        <v>Artificiais</v>
+        <f t="shared" ref="N3:O5" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+        <v>Agentes Artificiais</v>
       </c>
       <c r="O3" s="36" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Agente Artificial</v>
       </c>
       <c r="P3" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="Q3" s="37" t="s">
-        <v>108</v>
+      <c r="Q3" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara a un agente artificial</v>
       </c>
       <c r="R3" s="38" t="s">
         <v>10</v>
       </c>
       <c r="S3" s="38" t="str">
-        <f t="shared" ref="S3" si="7">SUBSTITUTE(C3, ".", " ")</f>
-        <v>Agênticos</v>
+        <f t="shared" ref="S3:S5" si="8">SUBSTITUTE(C3, ".", " ")</f>
+        <v>De Inteligência Projetual</v>
       </c>
       <c r="T3" s="38" t="str">
-        <f t="shared" ref="T3" si="8">SUBSTITUTE(D3, ".", " ")</f>
-        <v>Agentes</v>
+        <f t="shared" ref="T3:T5" si="9">SUBSTITUTE(D3, ".", " ")</f>
+        <v>Orquestações</v>
       </c>
       <c r="U3" s="38" t="str">
-        <f t="shared" ref="U3" si="9">SUBSTITUTE(E3, ".", " ")</f>
-        <v>Artificiais</v>
+        <f t="shared" ref="U3:U5" si="10">SUBSTITUTE(E3, ".", " ")</f>
+        <v>Agentes Artificiais</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="W3" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Key-AGEN-3</v>
       </c>
       <c r="X3" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Y3" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA3" s="37" t="s">
-        <v>106</v>
+        <v>10</v>
+      </c>
+      <c r="AA3" s="37" t="str">
+        <f t="shared" ref="AA3:AA13" si="11">_xlfn.TRANSLATE(P3,"pt","en")</f>
+        <v>Declares to an Artificial Agent</v>
       </c>
     </row>
     <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2345,16 +2329,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="F4" s="35" t="s">
         <v>102</v>
@@ -2375,81 +2359,82 @@
         <v>10</v>
       </c>
       <c r="L4" s="36" t="str">
-        <f t="shared" ref="L4:M5" si="10">CONCATENATE("", C4)</f>
-        <v>Agênticos</v>
+        <f t="shared" si="6"/>
+        <v>De.Inteligência.Projetual</v>
       </c>
       <c r="M4" s="36" t="str">
-        <f t="shared" ref="M4" si="11">CONCATENATE("", D4)</f>
-        <v>Agentes</v>
+        <f t="shared" si="6"/>
+        <v>Orquestações</v>
       </c>
       <c r="N4" s="36" t="str">
-        <f t="shared" ref="N4:O5" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
-        <v>Linguagens</v>
+        <f t="shared" si="7"/>
+        <v>Computacionais</v>
       </c>
       <c r="O4" s="36" t="str">
-        <f t="shared" ref="O4" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F4),"."," ")," De "," de "))</f>
+        <f t="shared" si="7"/>
         <v>Gherkin</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="Q4" s="37" t="str">
-        <f>_xlfn.TRANSLATE(P4,"pt","es")</f>
+        <f t="shared" si="3"/>
         <v>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</v>
       </c>
       <c r="R4" s="38" t="s">
         <v>10</v>
       </c>
       <c r="S4" s="38" t="str">
-        <f t="shared" ref="S4:U5" si="14">SUBSTITUTE(C4, ".", " ")</f>
-        <v>Agênticos</v>
+        <f t="shared" si="8"/>
+        <v>De Inteligência Projetual</v>
       </c>
       <c r="T4" s="38" t="str">
-        <f t="shared" ref="T4" si="15">SUBSTITUTE(D4, ".", " ")</f>
-        <v>Agentes</v>
+        <f t="shared" si="9"/>
+        <v>Orquestações</v>
       </c>
       <c r="U4" s="38" t="str">
-        <f t="shared" ref="U4" si="16">SUBSTITUTE(E4, ".", " ")</f>
-        <v>Linguagens</v>
+        <f t="shared" si="10"/>
+        <v>Computacionais</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="W4" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Key-AGEN-4</v>
       </c>
       <c r="X4" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Y4" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Z4" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA4" s="37" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares the Gherkin language, for BDD (Behaviour-Driven Development) processes.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>5</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>10</v>
@@ -2467,82 +2452,82 @@
         <v>10</v>
       </c>
       <c r="L5" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>De.Inteligência.Projetual</v>
+      </c>
+      <c r="M5" s="36" t="str">
+        <f t="shared" si="6"/>
+        <v>Orquestações</v>
+      </c>
+      <c r="N5" s="36" t="str">
+        <f t="shared" si="7"/>
+        <v>Computacionais</v>
+      </c>
+      <c r="O5" s="36" t="str">
+        <f t="shared" si="7"/>
+        <v>Sintática</v>
+      </c>
+      <c r="P5" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q5" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara una sintaxis computacional utilizada (por ejemplo, Manchester, TTL).</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S5" s="38" t="str">
+        <f t="shared" si="8"/>
+        <v>De Inteligência Projetual</v>
+      </c>
+      <c r="T5" s="38" t="str">
+        <f t="shared" si="9"/>
+        <v>Orquestações</v>
+      </c>
+      <c r="U5" s="38" t="str">
         <f t="shared" si="10"/>
-        <v>Inteligência</v>
-      </c>
-      <c r="M5" s="36" t="str">
-        <f t="shared" si="10"/>
-        <v>API</v>
-      </c>
-      <c r="N5" s="36" t="str">
-        <f t="shared" si="12"/>
-        <v>API Agentes</v>
-      </c>
-      <c r="O5" s="36" t="str">
-        <f t="shared" si="12"/>
-        <v>Agente</v>
-      </c>
-      <c r="P5" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q5" s="37" t="str">
-        <f t="shared" ref="Q5" si="17">_xlfn.TRANSLATE(P5,"pt","es")</f>
-        <v>Define un agente utilizado en el Proyecto.</v>
-      </c>
-      <c r="R5" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S5" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Inteligência</v>
-      </c>
-      <c r="T5" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>API</v>
-      </c>
-      <c r="U5" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>API Agentes</v>
+        <v>Computacionais</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="W5" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Key-AGEN-5</v>
       </c>
       <c r="X5" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Y5" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Z5" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="AA5" s="37" t="str">
-        <f t="shared" ref="AA5" si="18">_xlfn.TRANSLATE(P5,"pt","en")</f>
-        <v>Defines an agent used in the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="11"/>
+        <v>Declares a computational syntax used (e.g. Manchester, TTL).</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>6</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>10</v>
@@ -2560,62 +2545,62 @@
         <v>10</v>
       </c>
       <c r="L6" s="36" t="str">
-        <f t="shared" ref="L6:L7" si="19">CONCATENATE("", C6)</f>
-        <v>Inteligência</v>
+        <f t="shared" ref="L6:M10" si="12">CONCATENATE("", C6)</f>
+        <v>De.Inteligência.Projetual</v>
       </c>
       <c r="M6" s="36" t="str">
-        <f t="shared" ref="M6:M7" si="20">CONCATENATE("", D6)</f>
-        <v>API</v>
+        <f t="shared" ref="M6:M8" si="13">CONCATENATE("", D6)</f>
+        <v>Orquestações</v>
       </c>
       <c r="N6" s="36" t="str">
-        <f t="shared" ref="N6:N7" si="21">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
-        <v>API Agentes</v>
+        <f t="shared" ref="N6:O10" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
+        <v>Computacionais</v>
       </c>
       <c r="O6" s="36" t="str">
-        <f t="shared" ref="O6:O7" si="22">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F6),"."," ")," De "," de "))</f>
-        <v>Linguagem</v>
+        <f t="shared" ref="O6:O8" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F6),"."," ")," De "," de "))</f>
+        <v>Semântica</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="Q6" s="37" t="str">
-        <f t="shared" ref="Q6:Q7" si="23">_xlfn.TRANSLATE(P6,"pt","es")</f>
-        <v>Define un lenguaje utilizado para automatizar tareas de proyectos.</v>
-      </c>
-      <c r="R6" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S6" s="37" t="str">
-        <f t="shared" ref="S6:S7" si="24">SUBSTITUTE(C6, ".", " ")</f>
-        <v>Inteligência</v>
-      </c>
-      <c r="T6" s="37" t="str">
-        <f t="shared" ref="T6:T7" si="25">SUBSTITUTE(D6, ".", " ")</f>
-        <v>API</v>
-      </c>
-      <c r="U6" s="37" t="str">
-        <f t="shared" ref="U6:U7" si="26">SUBSTITUTE(E6, ".", " ")</f>
-        <v>API Agentes</v>
+        <f t="shared" si="3"/>
+        <v>Declara una semántica computacional utilizada (por ejemplo, KML, OKF, etc.).</v>
+      </c>
+      <c r="R6" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="S6" s="38" t="str">
+        <f t="shared" ref="S6:U10" si="16">SUBSTITUTE(C6, ".", " ")</f>
+        <v>De Inteligência Projetual</v>
+      </c>
+      <c r="T6" s="38" t="str">
+        <f t="shared" ref="T6:T8" si="17">SUBSTITUTE(D6, ".", " ")</f>
+        <v>Orquestações</v>
+      </c>
+      <c r="U6" s="38" t="str">
+        <f t="shared" ref="U6:U8" si="18">SUBSTITUTE(E6, ".", " ")</f>
+        <v>Computacionais</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="W6" s="52" t="str">
-        <f t="shared" ref="W6:W7" si="27">CONCATENATE("Key-AGEN-",A6)</f>
+        <f t="shared" si="5"/>
         <v>Key-AGEN-6</v>
       </c>
       <c r="X6" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Y6" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="Z6" s="37" t="s">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="AA6" s="37" t="str">
-        <f t="shared" ref="AA6:AA7" si="28">_xlfn.TRANSLATE(P6,"pt","en")</f>
-        <v>Defines a language used to automate project tasks.</v>
+        <f t="shared" si="11"/>
+        <v>Declares a computational semantics used (e.g. KML, OKF, etc).</v>
       </c>
     </row>
     <row r="7" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2623,20 +2608,20 @@
         <v>7</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="E7" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="F7" s="35" t="s">
-        <v>162</v>
-      </c>
       <c r="G7" s="58" t="s">
         <v>10</v>
       </c>
@@ -2653,103 +2638,656 @@
         <v>10</v>
       </c>
       <c r="L7" s="36" t="str">
-        <f t="shared" si="19"/>
-        <v>Inteligência</v>
+        <f t="shared" si="12"/>
+        <v>Inteligente</v>
       </c>
       <c r="M7" s="36" t="str">
-        <f t="shared" si="20"/>
-        <v>API</v>
+        <f t="shared" ref="M7" si="19">CONCATENATE("", D7)</f>
+        <v>Agêntica.Natural</v>
       </c>
       <c r="N7" s="36" t="str">
-        <f t="shared" si="21"/>
-        <v>API Agentes</v>
+        <f t="shared" si="14"/>
+        <v>Humanos</v>
       </c>
       <c r="O7" s="36" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="O7" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
+        <v>Projetista</v>
+      </c>
+      <c r="P7" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q7" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara un diseñador humano que trabaja en el proyecto.</v>
+      </c>
+      <c r="R7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S7" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="T7" s="37" t="str">
+        <f t="shared" ref="T7" si="21">SUBSTITUTE(D7, ".", " ")</f>
+        <v>Agêntica Natural</v>
+      </c>
+      <c r="U7" s="37" t="str">
+        <f t="shared" ref="U7" si="22">SUBSTITUTE(E7, ".", " ")</f>
+        <v>Humanos</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W7" s="52" t="str">
+        <f t="shared" ref="W7" si="23">CONCATENATE("Key-AGEN-",A7)</f>
+        <v>Key-AGEN-7</v>
+      </c>
+      <c r="X7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares a human designer working on the project.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33">
+        <v>8</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>190</v>
+      </c>
+      <c r="G8" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="36" t="str">
+        <f t="shared" ref="L8" si="24">CONCATENATE("", C8)</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="M8" s="36" t="str">
+        <f t="shared" si="13"/>
+        <v>Agêntica.Natural</v>
+      </c>
+      <c r="N8" s="36" t="str">
+        <f t="shared" ref="N8" si="25">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <v>Humanos</v>
+      </c>
+      <c r="O8" s="36" t="str">
+        <f t="shared" si="15"/>
+        <v>Calculista</v>
+      </c>
+      <c r="P8" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q8" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara una calculadora humana trabajando en el proyecto.</v>
+      </c>
+      <c r="R8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S8" s="37" t="str">
+        <f t="shared" ref="S8" si="26">SUBSTITUTE(C8, ".", " ")</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="T8" s="37" t="str">
+        <f t="shared" si="17"/>
+        <v>Agêntica Natural</v>
+      </c>
+      <c r="U8" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Humanos</v>
+      </c>
+      <c r="V8" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W8" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-AGEN-8</v>
+      </c>
+      <c r="X8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares a human calculator working on the project.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33">
+        <v>9</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M9" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N9" s="36" t="str">
+        <f t="shared" si="14"/>
+        <v>Artificiais</v>
+      </c>
+      <c r="O9" s="36" t="str">
+        <f t="shared" si="14"/>
+        <v>Agente IA</v>
+      </c>
+      <c r="P9" s="37" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q9" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara un agente artificial utilizado para el proyecto.</v>
+      </c>
+      <c r="R9" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="T9" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="U9" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Artificiais</v>
+      </c>
+      <c r="V9" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W9" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-AGEN-9</v>
+      </c>
+      <c r="X9" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares an artificial agent used for the project.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33">
+        <v>10</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M10" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N10" s="36" t="str">
+        <f t="shared" si="14"/>
+        <v>Linguagens</v>
+      </c>
+      <c r="O10" s="36" t="str">
+        <f t="shared" si="14"/>
+        <v>Idioma</v>
+      </c>
+      <c r="P10" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q10" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara un lenguaje natural utilizado en tareas de proyecto.</v>
+      </c>
+      <c r="R10" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S10" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="T10" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="U10" s="37" t="str">
+        <f t="shared" si="16"/>
+        <v>Linguagens</v>
+      </c>
+      <c r="V10" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W10" s="52" t="str">
+        <f t="shared" ref="W10" si="27">CONCATENATE("Key-AGEN-",A10)</f>
+        <v>Key-AGEN-10</v>
+      </c>
+      <c r="X10" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares a natural language used in project tasks.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="33">
+        <v>11</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="36" t="str">
+        <f t="shared" ref="L11:L12" si="28">CONCATENATE("", C11)</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="M11" s="36" t="str">
+        <f t="shared" ref="M11:M12" si="29">CONCATENATE("", D11)</f>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N11" s="36" t="str">
+        <f t="shared" ref="N11:N12" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <v>Linguagens</v>
+      </c>
+      <c r="O11" s="36" t="str">
+        <f t="shared" ref="O11:O12" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F11),"."," ")," De "," de "))</f>
+        <v>Linguagem</v>
+      </c>
+      <c r="P11" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q11" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara un lenguaje de ordenador utilizado para automatizar tareas de proyecto.</v>
+      </c>
+      <c r="R11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S11" s="37" t="str">
+        <f t="shared" ref="S11:S12" si="32">SUBSTITUTE(C11, ".", " ")</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="T11" s="37" t="str">
+        <f t="shared" ref="T11:T12" si="33">SUBSTITUTE(D11, ".", " ")</f>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="U11" s="37" t="str">
+        <f t="shared" ref="U11:U12" si="34">SUBSTITUTE(E11, ".", " ")</f>
+        <v>Linguagens</v>
+      </c>
+      <c r="V11" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W11" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-AGEN-11</v>
+      </c>
+      <c r="X11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares a computer language used to automate project tasks.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="33">
+        <v>12</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="G12" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="36" t="str">
+        <f t="shared" si="28"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M12" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N12" s="36" t="str">
+        <f t="shared" si="30"/>
+        <v>Linguagens</v>
+      </c>
+      <c r="O12" s="36" t="str">
+        <f t="shared" si="31"/>
         <v>Sintaxe</v>
       </c>
-      <c r="P7" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q7" s="37" t="str">
-        <f t="shared" si="23"/>
-        <v>Define una sintaxis utilizada para automatizar tareas del proyecto.</v>
-      </c>
-      <c r="R7" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S7" s="37" t="str">
-        <f t="shared" si="24"/>
-        <v>Inteligência</v>
-      </c>
-      <c r="T7" s="37" t="str">
-        <f t="shared" si="25"/>
-        <v>API</v>
-      </c>
-      <c r="U7" s="37" t="str">
-        <f t="shared" si="26"/>
-        <v>API Agentes</v>
-      </c>
-      <c r="V7" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="W7" s="52" t="str">
-        <f t="shared" si="27"/>
-        <v>Key-AGEN-7</v>
-      </c>
-      <c r="X7" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y7" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z7" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA7" s="37" t="str">
-        <f t="shared" si="28"/>
-        <v>Defines a syntax used to automate project tasks.</v>
+      <c r="P12" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q12" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara una sintaxis artificial usada para automatizar tareas del proyecto.</v>
+      </c>
+      <c r="R12" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S12" s="37" t="str">
+        <f t="shared" si="32"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="T12" s="37" t="str">
+        <f t="shared" si="33"/>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="U12" s="37" t="str">
+        <f t="shared" si="34"/>
+        <v>Linguagens</v>
+      </c>
+      <c r="V12" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W12" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-AGEN-12</v>
+      </c>
+      <c r="X12" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y12" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares an artificial syntax used to automate project tasks.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33">
+        <v>13</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="G13" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="36" t="str">
+        <f t="shared" ref="L13" si="35">CONCATENATE("", C13)</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="M13" s="36" t="str">
+        <f t="shared" ref="M13" si="36">CONCATENATE("", D13)</f>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N13" s="36" t="str">
+        <f t="shared" ref="N13" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
+        <v>Linguagens</v>
+      </c>
+      <c r="O13" s="36" t="str">
+        <f t="shared" ref="O13" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F13),"."," ")," De "," de "))</f>
+        <v>Semântico</v>
+      </c>
+      <c r="P13" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q13" s="37" t="str">
+        <f t="shared" si="3"/>
+        <v>Declara una semántica específica usada para dar significado a los elementos del proyecto.</v>
+      </c>
+      <c r="R13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="S13" s="37" t="str">
+        <f t="shared" ref="S13" si="39">SUBSTITUTE(C13, ".", " ")</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="T13" s="37" t="str">
+        <f t="shared" ref="T13" si="40">SUBSTITUTE(D13, ".", " ")</f>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="U13" s="37" t="str">
+        <f t="shared" ref="U13" si="41">SUBSTITUTE(E13, ".", " ")</f>
+        <v>Linguagens</v>
+      </c>
+      <c r="V13" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="W13" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-AGEN-13</v>
+      </c>
+      <c r="X13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Declares a specific semantics used to give meaning to the elements of the project.</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA1:AA2 A2:B2 B3:B4 A3:A7">
-    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F4 F8:F1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4 AA3:XFD3 L3:O4 AB4:XFD4">
-    <cfRule type="cellIs" dxfId="24" priority="75" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4">
-    <cfRule type="duplicateValues" dxfId="23" priority="630"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="663"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="664"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="665"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="672"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B5:B7">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F7">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA5:AA7">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B13">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6 L3:O6 AB3:XFD6">
+    <cfRule type="cellIs" dxfId="13" priority="78" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="12" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="675"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F13">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F1048576 F1:F6">
+    <cfRule type="duplicateValues" dxfId="4" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA13">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2953,7 +3491,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2964,30 +3502,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" style="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="42" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="40" customWidth="1"/>
     <col min="4" max="4" width="5.85546875" style="40" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="40" customWidth="1"/>
-    <col min="6" max="6" width="3.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="40" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="40" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" style="40" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="40" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" style="40" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="40" customWidth="1"/>
-    <col min="16" max="16" width="5.140625" style="40" customWidth="1"/>
-    <col min="17" max="17" width="49.5703125" style="40" customWidth="1"/>
-    <col min="18" max="16384" width="9.28515625" style="40"/>
+    <col min="5" max="5" width="5.42578125" style="40" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" style="40" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" style="40" customWidth="1"/>
+    <col min="8" max="8" width="3.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.85546875" style="40" customWidth="1"/>
+    <col min="10" max="10" width="5.85546875" style="40" customWidth="1"/>
+    <col min="11" max="12" width="9.7109375" style="40" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="40" customWidth="1"/>
+    <col min="14" max="14" width="8.28515625" style="40" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" style="40" customWidth="1"/>
+    <col min="16" max="16" width="3.5703125" style="40" customWidth="1"/>
+    <col min="17" max="17" width="9" style="40" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="40" customWidth="1"/>
+    <col min="19" max="19" width="47.5703125" style="40" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="54" customWidth="1"/>
+    <col min="21" max="21" width="39" style="54" customWidth="1"/>
+    <col min="22" max="22" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="54" customWidth="1"/>
+    <col min="24" max="24" width="5.7109375" style="54" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" style="50" customWidth="1"/>
+    <col min="26" max="16384" width="9.28515625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
         <v>11</v>
       </c>
@@ -3003,13 +3548,9 @@
       <c r="E1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="22" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="24" t="s">
         <v>75</v>
       </c>
       <c r="I1" s="22" t="s">
@@ -3039,433 +3580,731 @@
       <c r="Q1" s="22" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="T1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="U1" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="V1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="W1" s="60" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="60" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49">
         <v>2</v>
       </c>
       <c r="B2" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q2" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="56" t="s">
+      <c r="R2" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="I2" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="J2" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="K2" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="P2" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T2" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="U2" s="64" t="s">
+        <v>160</v>
+      </c>
+      <c r="V2" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="W2" s="65" t="s">
+        <v>162</v>
+      </c>
+      <c r="X2" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y2" s="66" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="49">
         <v>3</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F3" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="H3" s="29" t="s">
-        <v>149</v>
-      </c>
       <c r="I3" s="23" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="M3" s="23" t="s">
-        <v>137</v>
+        <v>10</v>
       </c>
       <c r="N3" s="29" t="s">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="P3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q3" s="23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S3" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="T3" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V3" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y3" s="66" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49">
         <v>4</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F4" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H4" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>149</v>
-      </c>
       <c r="I4" s="23" t="s">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>126</v>
+        <v>10</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="M4" s="23" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>116</v>
+        <v>10</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>123</v>
+        <v>10</v>
       </c>
       <c r="P4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q4" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S4" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="T4" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V4" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X4" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y4" s="66" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="49">
         <v>5</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F5" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>149</v>
-      </c>
       <c r="I5" s="23" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="L5" s="29" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="O5" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="P5" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q5" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="S5" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="P5" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q5" s="23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T5" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V5" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y5" s="66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49">
         <v>6</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="I6" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="K6" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>131</v>
-      </c>
       <c r="L6" s="29" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="P6" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="R6" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q6" s="23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S6" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="T6" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V6" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X6" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y6" s="66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
         <v>7</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F7" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H7" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="I7" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="P7" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="N7" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="P7" s="29" t="s">
+      <c r="Q7" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="R7" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q7" s="23" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S7" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="T7" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V7" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X7" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y7" s="66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>8</v>
       </c>
       <c r="B8" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F8" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="39" t="s">
+      <c r="G8" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="K8" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F8" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>10</v>
-      </c>
       <c r="L8" s="29" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="P8" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="R8" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q8" s="23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S8" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="T8" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V8" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X8" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y8" s="66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>9</v>
       </c>
       <c r="B9" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F9" s="56" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="G9" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q9" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="R9" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="S9" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="T9" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V9" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y9" s="66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="49">
+        <v>10</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="F10" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="57" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="O10" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="N9" s="29" t="s">
+      <c r="P10" s="29" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q10" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="O9" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="P9" s="29" t="s">
+      <c r="R10" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q9" s="23" t="s">
-        <v>144</v>
+      <c r="S10" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="T10" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V10" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X10" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y10" s="66" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="T1:Y10">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Versão5/PRO/Ontologia_Agentes.xlsx
+++ b/Versão5/PRO/Ontologia_Agentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F1C917-98E1-4B61-9BC0-2A094EC4056F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC9D191-447E-4DBA-B1F9-DCDFA4DDB550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="224">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -313,12 +313,6 @@
     <t>Equivalente a</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -662,6 +656,93 @@
   </si>
   <si>
     <t>Declara uma sintaxe computacional utilizada (ex. Manchester, TTL).</t>
+  </si>
+  <si>
+    <t>Declares to a Human Agent</t>
+  </si>
+  <si>
+    <t>Declares to an Artificial Agent</t>
+  </si>
+  <si>
+    <t>Declares the Gherkin language, for BDD (Behaviour-Driven Development) processes.</t>
+  </si>
+  <si>
+    <t>Declares a computational syntax used (e.g. Manchester, TTL).</t>
+  </si>
+  <si>
+    <t>Declares a computational semantics used (e.g. KML, OKF, etc).</t>
+  </si>
+  <si>
+    <t>Declares a human designer working on the project.</t>
+  </si>
+  <si>
+    <t>Declares a human calculator working on the project.</t>
+  </si>
+  <si>
+    <t>Declares an artificial agent used for the project.</t>
+  </si>
+  <si>
+    <t>Declares a natural language used in project tasks.</t>
+  </si>
+  <si>
+    <t>Declares a computer language used to automate project tasks.</t>
+  </si>
+  <si>
+    <t>Declares an artificial syntax used to automate project tasks.</t>
+  </si>
+  <si>
+    <t>Declares a specific semantics used to give meaning to the elements of the project.</t>
+  </si>
+  <si>
+    <t>Declara a un agente humano</t>
+  </si>
+  <si>
+    <t>Declara a un agente artificial</t>
+  </si>
+  <si>
+    <t>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</t>
+  </si>
+  <si>
+    <t>Declara una sintaxis computacional utilizada (por ejemplo, Manchester, TTL).</t>
+  </si>
+  <si>
+    <t>Declara una semántica computacional utilizada (por ejemplo, KML, OKF, etc.).</t>
+  </si>
+  <si>
+    <t>Declara un diseñador humano que trabaja en el proyecto.</t>
+  </si>
+  <si>
+    <t>Declara una calculadora humana trabajando en el proyecto.</t>
+  </si>
+  <si>
+    <t>Declara un agente artificial utilizado para el proyecto.</t>
+  </si>
+  <si>
+    <t>Declara un lenguaje natural utilizado en tareas de proyecto.</t>
+  </si>
+  <si>
+    <t>Declara un lenguaje de ordenador utilizado para automatizar tareas de proyecto.</t>
+  </si>
+  <si>
+    <t>Declara una sintaxis artificial usada para automatizar tareas del proyecto.</t>
+  </si>
+  <si>
+    <t>Declara una semántica específica usada para dar significado a los elementos del proyecto.</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
   </si>
 </sst>
 </file>
@@ -1717,15 +1798,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="54" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.28515625" style="54"/>
+    <col min="1" max="1" width="9.3046875" style="54" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.3046875" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>46</v>
       </c>
@@ -1733,10 +1814,10 @@
         <v>47</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
@@ -1744,21 +1825,21 @@
         <v>49</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
         <v>51</v>
       </c>
@@ -1766,10 +1847,10 @@
         <v>33</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
         <v>52</v>
       </c>
@@ -1778,10 +1859,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
@@ -1790,10 +1871,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
         <v>54</v>
       </c>
@@ -1801,21 +1882,21 @@
         <v>55</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
         <v>57</v>
       </c>
@@ -1823,10 +1904,10 @@
         <v>58</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
         <v>59</v>
       </c>
@@ -1834,10 +1915,10 @@
         <v>60</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
         <v>61</v>
       </c>
@@ -1845,10 +1926,10 @@
         <v>60</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
         <v>62</v>
       </c>
@@ -1856,10 +1937,10 @@
         <v>60</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
         <v>63</v>
       </c>
@@ -1867,10 +1948,10 @@
         <v>60</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
         <v>64</v>
       </c>
@@ -1878,10 +1959,10 @@
         <v>60</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
         <v>65</v>
       </c>
@@ -1889,10 +1970,10 @@
         <v>60</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>66</v>
       </c>
@@ -1900,68 +1981,68 @@
         <v>60</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="20">
         <f ca="1">NOW()</f>
-        <v>46248.624910763887</v>
+        <v>46253.798913078703</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B20" s="20" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B21" s="20" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
@@ -1969,10 +2050,10 @@
         <v>60</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
         <v>70</v>
       </c>
@@ -1980,21 +2061,21 @@
         <v>60</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
         <v>71</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
         <v>72</v>
       </c>
@@ -2003,19 +2084,19 @@
         <v>Formaliza las clases para agentes.</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B26" s="21" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize agent classes.</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2026,36 +2107,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AC13"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" style="13" customWidth="1"/>
-    <col min="7" max="11" width="7.7109375" style="13" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" style="13" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="12" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9.140625" style="2" customWidth="1"/>
-    <col min="16" max="16" width="37.5703125" style="13" customWidth="1"/>
-    <col min="17" max="17" width="42.85546875" style="13" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.7109375" style="53" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.85546875" style="32" customWidth="1"/>
-    <col min="25" max="25" width="6.5703125" style="32" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.140625" style="31" customWidth="1"/>
-    <col min="27" max="27" width="45.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="1.4609375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.61328125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.4609375" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.765625" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.23046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.61328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.765625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.4609375" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.07421875" style="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="32" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="32" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="31" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="3" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="28" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26">
         <v>0</v>
       </c>
@@ -2107,55 +2190,61 @@
       <c r="Q1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="55" t="s">
+      <c r="R1" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="S1" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="T1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="T1" s="16" t="s">
+      <c r="U1" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="V1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="V1" s="16" t="s">
+      <c r="W1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="X1" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="Y1" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z1" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA1" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB1" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC1" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z1" s="47" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA1" s="43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="33">
         <v>2</v>
       </c>
       <c r="B2" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F2" s="35" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>10</v>
@@ -2189,66 +2278,70 @@
         <v>Agente Humano</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q2" s="37" t="str">
-        <f t="shared" ref="Q2:Q13" si="3">_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Declara a un agente humano</v>
-      </c>
-      <c r="R2" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="38" t="str">
-        <f t="shared" ref="S2:U2" si="4">SUBSTITUTE(C2, ".", " ")</f>
+        <v>101</v>
+      </c>
+      <c r="Q2" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="R2" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" s="38" t="str">
+        <f t="shared" ref="T2:V2" si="3">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="T2" s="38" t="str">
-        <f t="shared" si="4"/>
+      <c r="U2" s="38" t="str">
+        <f t="shared" si="3"/>
         <v>Orquestações</v>
       </c>
-      <c r="U2" s="38" t="str">
-        <f t="shared" si="4"/>
+      <c r="V2" s="38" t="str">
+        <f t="shared" si="3"/>
         <v>Agentes Humanos</v>
       </c>
-      <c r="V2" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W2" s="52" t="str">
-        <f t="shared" ref="W2:W13" si="5">CONCATENATE("Key-AGEN-",A2)</f>
+      <c r="W2" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X2" s="52" t="str">
+        <f t="shared" ref="X2:X13" si="4">CONCATENATE("Key-AGEN-",A2)</f>
         <v>Key-AGEN-2</v>
       </c>
-      <c r="X2" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y2" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z2" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA2" s="37" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Declares to a Human Agent</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA2" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB2" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC2" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="33">
         <v>3</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D3" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="34" t="s">
-        <v>171</v>
-      </c>
       <c r="F3" s="35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G3" s="58" t="s">
         <v>10</v>
@@ -2266,82 +2359,86 @@
         <v>10</v>
       </c>
       <c r="L3" s="36" t="str">
-        <f t="shared" ref="L3:M5" si="6">CONCATENATE("", C3)</f>
+        <f t="shared" ref="L3:M5" si="5">CONCATENATE("", C3)</f>
         <v>De.Inteligência.Projetual</v>
       </c>
       <c r="M3" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>Orquestações</v>
+      </c>
+      <c r="N3" s="36" t="str">
+        <f t="shared" ref="N3:O5" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+        <v>Agentes Artificiais</v>
+      </c>
+      <c r="O3" s="36" t="str">
         <f t="shared" si="6"/>
+        <v>Agente Artificial</v>
+      </c>
+      <c r="P3" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q3" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="R3" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="S3" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="38" t="str">
+        <f t="shared" ref="T3:T5" si="7">SUBSTITUTE(C3, ".", " ")</f>
+        <v>De Inteligência Projetual</v>
+      </c>
+      <c r="U3" s="38" t="str">
+        <f t="shared" ref="U3:U5" si="8">SUBSTITUTE(D3, ".", " ")</f>
         <v>Orquestações</v>
       </c>
-      <c r="N3" s="36" t="str">
-        <f t="shared" ref="N3:O5" si="7">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
+      <c r="V3" s="38" t="str">
+        <f t="shared" ref="V3:V5" si="9">SUBSTITUTE(E3, ".", " ")</f>
         <v>Agentes Artificiais</v>
       </c>
-      <c r="O3" s="36" t="str">
-        <f t="shared" si="7"/>
-        <v>Agente Artificial</v>
-      </c>
-      <c r="P3" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q3" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara a un agente artificial</v>
-      </c>
-      <c r="R3" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S3" s="38" t="str">
-        <f t="shared" ref="S3:S5" si="8">SUBSTITUTE(C3, ".", " ")</f>
-        <v>De Inteligência Projetual</v>
-      </c>
-      <c r="T3" s="38" t="str">
-        <f t="shared" ref="T3:T5" si="9">SUBSTITUTE(D3, ".", " ")</f>
-        <v>Orquestações</v>
-      </c>
-      <c r="U3" s="38" t="str">
-        <f t="shared" ref="U3:U5" si="10">SUBSTITUTE(E3, ".", " ")</f>
-        <v>Agentes Artificiais</v>
-      </c>
-      <c r="V3" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W3" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W3" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X3" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-3</v>
       </c>
-      <c r="X3" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y3" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z3" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="37" t="str">
-        <f t="shared" ref="AA3:AA13" si="11">_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Declares to an Artificial Agent</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA3" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB3" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC3" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="33">
         <v>4</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D4" s="34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>10</v>
@@ -2359,82 +2456,86 @@
         <v>10</v>
       </c>
       <c r="L4" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>De.Inteligência.Projetual</v>
+      </c>
+      <c r="M4" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>Orquestações</v>
+      </c>
+      <c r="N4" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>De.Inteligência.Projetual</v>
-      </c>
-      <c r="M4" s="36" t="str">
+        <v>Computacionais</v>
+      </c>
+      <c r="O4" s="36" t="str">
         <f t="shared" si="6"/>
+        <v>Gherkin</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q4" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="R4" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="S4" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" s="38" t="str">
+        <f t="shared" si="7"/>
+        <v>De Inteligência Projetual</v>
+      </c>
+      <c r="U4" s="38" t="str">
+        <f t="shared" si="8"/>
         <v>Orquestações</v>
       </c>
-      <c r="N4" s="36" t="str">
-        <f t="shared" si="7"/>
+      <c r="V4" s="38" t="str">
+        <f t="shared" si="9"/>
         <v>Computacionais</v>
       </c>
-      <c r="O4" s="36" t="str">
-        <f t="shared" si="7"/>
-        <v>Gherkin</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q4" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara el lenguaje Gherkin, para procesos BDD (Desarrollo Impulsado por el Comportamiento).</v>
-      </c>
-      <c r="R4" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S4" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v>De Inteligência Projetual</v>
-      </c>
-      <c r="T4" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v>Orquestações</v>
-      </c>
-      <c r="U4" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Computacionais</v>
-      </c>
-      <c r="V4" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W4" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W4" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X4" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-4</v>
       </c>
-      <c r="X4" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y4" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z4" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares the Gherkin language, for BDD (Behaviour-Driven Development) processes.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA4" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB4" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC4" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="33">
         <v>5</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" s="35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>10</v>
@@ -2452,82 +2553,86 @@
         <v>10</v>
       </c>
       <c r="L5" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>De.Inteligência.Projetual</v>
+      </c>
+      <c r="M5" s="36" t="str">
+        <f t="shared" si="5"/>
+        <v>Orquestações</v>
+      </c>
+      <c r="N5" s="36" t="str">
         <f t="shared" si="6"/>
-        <v>De.Inteligência.Projetual</v>
-      </c>
-      <c r="M5" s="36" t="str">
+        <v>Computacionais</v>
+      </c>
+      <c r="O5" s="36" t="str">
         <f t="shared" si="6"/>
+        <v>Sintática</v>
+      </c>
+      <c r="P5" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q5" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="R5" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="S5" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="T5" s="38" t="str">
+        <f t="shared" si="7"/>
+        <v>De Inteligência Projetual</v>
+      </c>
+      <c r="U5" s="38" t="str">
+        <f t="shared" si="8"/>
         <v>Orquestações</v>
       </c>
-      <c r="N5" s="36" t="str">
-        <f t="shared" si="7"/>
+      <c r="V5" s="38" t="str">
+        <f t="shared" si="9"/>
         <v>Computacionais</v>
       </c>
-      <c r="O5" s="36" t="str">
-        <f t="shared" si="7"/>
-        <v>Sintática</v>
-      </c>
-      <c r="P5" s="37" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q5" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara una sintaxis computacional utilizada (por ejemplo, Manchester, TTL).</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S5" s="38" t="str">
-        <f t="shared" si="8"/>
-        <v>De Inteligência Projetual</v>
-      </c>
-      <c r="T5" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v>Orquestações</v>
-      </c>
-      <c r="U5" s="38" t="str">
-        <f t="shared" si="10"/>
-        <v>Computacionais</v>
-      </c>
-      <c r="V5" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W5" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W5" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X5" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-5</v>
       </c>
-      <c r="X5" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y5" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z5" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a computational syntax used (e.g. Manchester, TTL).</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA5" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB5" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC5" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="33">
         <v>6</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>10</v>
@@ -2545,82 +2650,86 @@
         <v>10</v>
       </c>
       <c r="L6" s="36" t="str">
-        <f t="shared" ref="L6:M10" si="12">CONCATENATE("", C6)</f>
+        <f t="shared" ref="L6:M10" si="10">CONCATENATE("", C6)</f>
         <v>De.Inteligência.Projetual</v>
       </c>
       <c r="M6" s="36" t="str">
-        <f t="shared" ref="M6:M8" si="13">CONCATENATE("", D6)</f>
+        <f t="shared" ref="M6:M8" si="11">CONCATENATE("", D6)</f>
         <v>Orquestações</v>
       </c>
       <c r="N6" s="36" t="str">
-        <f t="shared" ref="N6:O10" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N6:O10" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
         <v>Computacionais</v>
       </c>
       <c r="O6" s="36" t="str">
-        <f t="shared" ref="O6:O8" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F6),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O6:O8" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F6),"."," ")," De "," de "))</f>
         <v>Semântica</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>195</v>
-      </c>
-      <c r="Q6" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara una semántica computacional utilizada (por ejemplo, KML, OKF, etc.).</v>
-      </c>
-      <c r="R6" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="S6" s="38" t="str">
-        <f t="shared" ref="S6:U10" si="16">SUBSTITUTE(C6, ".", " ")</f>
+        <v>193</v>
+      </c>
+      <c r="Q6" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="R6" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="S6" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="T6" s="38" t="str">
+        <f t="shared" ref="T6:V10" si="14">SUBSTITUTE(C6, ".", " ")</f>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="T6" s="38" t="str">
-        <f t="shared" ref="T6:T8" si="17">SUBSTITUTE(D6, ".", " ")</f>
+      <c r="U6" s="38" t="str">
+        <f t="shared" ref="U6:U8" si="15">SUBSTITUTE(D6, ".", " ")</f>
         <v>Orquestações</v>
       </c>
-      <c r="U6" s="38" t="str">
-        <f t="shared" ref="U6:U8" si="18">SUBSTITUTE(E6, ".", " ")</f>
+      <c r="V6" s="38" t="str">
+        <f t="shared" ref="V6:V8" si="16">SUBSTITUTE(E6, ".", " ")</f>
         <v>Computacionais</v>
       </c>
-      <c r="V6" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W6" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W6" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X6" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-6</v>
       </c>
-      <c r="X6" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y6" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z6" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a computational semantics used (e.g. KML, OKF, etc).</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA6" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB6" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC6" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="33">
         <v>7</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>10</v>
@@ -2638,82 +2747,86 @@
         <v>10</v>
       </c>
       <c r="L7" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M7" s="36" t="str">
+        <f t="shared" ref="M7" si="17">CONCATENATE("", D7)</f>
+        <v>Agêntica.Natural</v>
+      </c>
+      <c r="N7" s="36" t="str">
         <f t="shared" si="12"/>
+        <v>Humanos</v>
+      </c>
+      <c r="O7" s="36" t="str">
+        <f t="shared" ref="O7" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
+        <v>Projetista</v>
+      </c>
+      <c r="P7" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q7" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="R7" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="S7" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T7" s="37" t="str">
+        <f t="shared" si="14"/>
         <v>Inteligente</v>
       </c>
-      <c r="M7" s="36" t="str">
-        <f t="shared" ref="M7" si="19">CONCATENATE("", D7)</f>
-        <v>Agêntica.Natural</v>
-      </c>
-      <c r="N7" s="36" t="str">
-        <f t="shared" si="14"/>
+      <c r="U7" s="37" t="str">
+        <f t="shared" ref="U7" si="19">SUBSTITUTE(D7, ".", " ")</f>
+        <v>Agêntica Natural</v>
+      </c>
+      <c r="V7" s="37" t="str">
+        <f t="shared" ref="V7" si="20">SUBSTITUTE(E7, ".", " ")</f>
         <v>Humanos</v>
       </c>
-      <c r="O7" s="36" t="str">
-        <f t="shared" ref="O7" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
-        <v>Projetista</v>
-      </c>
-      <c r="P7" s="37" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q7" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara un diseñador humano que trabaja en el proyecto.</v>
-      </c>
-      <c r="R7" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S7" s="37" t="str">
-        <f t="shared" si="16"/>
-        <v>Inteligente</v>
-      </c>
-      <c r="T7" s="37" t="str">
-        <f t="shared" ref="T7" si="21">SUBSTITUTE(D7, ".", " ")</f>
-        <v>Agêntica Natural</v>
-      </c>
-      <c r="U7" s="37" t="str">
-        <f t="shared" ref="U7" si="22">SUBSTITUTE(E7, ".", " ")</f>
-        <v>Humanos</v>
-      </c>
-      <c r="V7" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W7" s="52" t="str">
-        <f t="shared" ref="W7" si="23">CONCATENATE("Key-AGEN-",A7)</f>
+      <c r="W7" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X7" s="52" t="str">
+        <f t="shared" ref="X7" si="21">CONCATENATE("Key-AGEN-",A7)</f>
         <v>Key-AGEN-7</v>
       </c>
-      <c r="X7" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y7" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z7" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a human designer working on the project.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA7" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB7" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC7" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="33">
         <v>8</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="35" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>10</v>
@@ -2731,268 +2844,280 @@
         <v>10</v>
       </c>
       <c r="L8" s="36" t="str">
-        <f t="shared" ref="L8" si="24">CONCATENATE("", C8)</f>
+        <f t="shared" ref="L8" si="22">CONCATENATE("", C8)</f>
         <v>Inteligente</v>
       </c>
       <c r="M8" s="36" t="str">
+        <f t="shared" si="11"/>
+        <v>Agêntica.Natural</v>
+      </c>
+      <c r="N8" s="36" t="str">
+        <f t="shared" ref="N8" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <v>Humanos</v>
+      </c>
+      <c r="O8" s="36" t="str">
         <f t="shared" si="13"/>
-        <v>Agêntica.Natural</v>
-      </c>
-      <c r="N8" s="36" t="str">
-        <f t="shared" ref="N8" si="25">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
+        <v>Calculista</v>
+      </c>
+      <c r="P8" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q8" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="R8" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="S8" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T8" s="37" t="str">
+        <f t="shared" ref="T8" si="24">SUBSTITUTE(C8, ".", " ")</f>
+        <v>Inteligente</v>
+      </c>
+      <c r="U8" s="37" t="str">
+        <f t="shared" si="15"/>
+        <v>Agêntica Natural</v>
+      </c>
+      <c r="V8" s="37" t="str">
+        <f t="shared" si="16"/>
         <v>Humanos</v>
       </c>
-      <c r="O8" s="36" t="str">
-        <f t="shared" si="15"/>
-        <v>Calculista</v>
-      </c>
-      <c r="P8" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q8" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara una calculadora humana trabajando en el proyecto.</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S8" s="37" t="str">
-        <f t="shared" ref="S8" si="26">SUBSTITUTE(C8, ".", " ")</f>
-        <v>Inteligente</v>
-      </c>
-      <c r="T8" s="37" t="str">
-        <f t="shared" si="17"/>
-        <v>Agêntica Natural</v>
-      </c>
-      <c r="U8" s="37" t="str">
-        <f t="shared" si="18"/>
-        <v>Humanos</v>
-      </c>
-      <c r="V8" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W8" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W8" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X8" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-8</v>
       </c>
-      <c r="X8" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y8" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z8" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA8" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a human calculator working on the project.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA8" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB8" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC8" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="33">
         <v>9</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C9" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F9" s="35" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M9" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N9" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Artificiais</v>
+      </c>
+      <c r="O9" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Agente IA</v>
+      </c>
+      <c r="P9" s="37" t="s">
         <v>176</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="36" t="str">
-        <f t="shared" si="12"/>
+      <c r="Q9" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="R9" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="S9" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T9" s="37" t="str">
+        <f t="shared" si="14"/>
         <v>Inteligente</v>
       </c>
-      <c r="M9" s="36" t="str">
-        <f t="shared" si="12"/>
-        <v>Agêntica.Artificial</v>
-      </c>
-      <c r="N9" s="36" t="str">
+      <c r="U9" s="37" t="str">
+        <f t="shared" si="14"/>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="V9" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Artificiais</v>
       </c>
-      <c r="O9" s="36" t="str">
+      <c r="W9" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X9" s="52" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-9</v>
+      </c>
+      <c r="Y9" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z9" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA9" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB9" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC9" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="33">
+        <v>10</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M10" s="36" t="str">
+        <f t="shared" si="10"/>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N10" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Linguagens</v>
+      </c>
+      <c r="O10" s="36" t="str">
+        <f t="shared" si="12"/>
+        <v>Idioma</v>
+      </c>
+      <c r="P10" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q10" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="R10" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="S10" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T10" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Agente IA</v>
-      </c>
-      <c r="P9" s="37" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q9" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara un agente artificial utilizado para el proyecto.</v>
-      </c>
-      <c r="R9" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" s="37" t="str">
-        <f t="shared" si="16"/>
         <v>Inteligente</v>
       </c>
-      <c r="T9" s="37" t="str">
-        <f t="shared" si="16"/>
+      <c r="U10" s="37" t="str">
+        <f t="shared" si="14"/>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="U9" s="37" t="str">
-        <f t="shared" si="16"/>
-        <v>Artificiais</v>
-      </c>
-      <c r="V9" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W9" s="52" t="str">
-        <f t="shared" si="5"/>
-        <v>Key-AGEN-9</v>
-      </c>
-      <c r="X9" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y9" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares an artificial agent used for the project.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33">
-        <v>10</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="36" t="str">
-        <f t="shared" si="12"/>
-        <v>Inteligente</v>
-      </c>
-      <c r="M10" s="36" t="str">
-        <f t="shared" si="12"/>
-        <v>Agêntica.Artificial</v>
-      </c>
-      <c r="N10" s="36" t="str">
+      <c r="V10" s="37" t="str">
         <f t="shared" si="14"/>
         <v>Linguagens</v>
       </c>
-      <c r="O10" s="36" t="str">
-        <f t="shared" si="14"/>
-        <v>Idioma</v>
-      </c>
-      <c r="P10" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q10" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara un lenguaje natural utilizado en tareas de proyecto.</v>
-      </c>
-      <c r="R10" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S10" s="37" t="str">
-        <f t="shared" si="16"/>
-        <v>Inteligente</v>
-      </c>
-      <c r="T10" s="37" t="str">
-        <f t="shared" si="16"/>
-        <v>Agêntica Artificial</v>
-      </c>
-      <c r="U10" s="37" t="str">
-        <f t="shared" si="16"/>
-        <v>Linguagens</v>
-      </c>
-      <c r="V10" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W10" s="52" t="str">
-        <f t="shared" ref="W10" si="27">CONCATENATE("Key-AGEN-",A10)</f>
+      <c r="W10" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X10" s="52" t="str">
+        <f t="shared" ref="X10" si="25">CONCATENATE("Key-AGEN-",A10)</f>
         <v>Key-AGEN-10</v>
       </c>
-      <c r="X10" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y10" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z10" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA10" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a natural language used in project tasks.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA10" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB10" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC10" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="33">
         <v>11</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>10</v>
@@ -3010,83 +3135,87 @@
         <v>10</v>
       </c>
       <c r="L11" s="36" t="str">
-        <f t="shared" ref="L11:L12" si="28">CONCATENATE("", C11)</f>
+        <f t="shared" ref="L11:L12" si="26">CONCATENATE("", C11)</f>
         <v>Inteligente</v>
       </c>
       <c r="M11" s="36" t="str">
-        <f t="shared" ref="M11:M12" si="29">CONCATENATE("", D11)</f>
+        <f t="shared" ref="M11:M12" si="27">CONCATENATE("", D11)</f>
         <v>Agêntica.Artificial</v>
       </c>
       <c r="N11" s="36" t="str">
-        <f t="shared" ref="N11:N12" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N11:N12" si="28">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Linguagens</v>
       </c>
       <c r="O11" s="36" t="str">
-        <f t="shared" ref="O11:O12" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F11),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O11:O12" si="29">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F11),"."," ")," De "," de "))</f>
         <v>Linguagem</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q11" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara un lenguaje de ordenador utilizado para automatizar tareas de proyecto.</v>
+        <v>190</v>
+      </c>
+      <c r="Q11" s="37" t="s">
+        <v>216</v>
       </c>
       <c r="R11" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" s="37" t="str">
-        <f t="shared" ref="S11:S12" si="32">SUBSTITUTE(C11, ".", " ")</f>
+        <v>204</v>
+      </c>
+      <c r="S11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T11" s="37" t="str">
+        <f t="shared" ref="T11:T12" si="30">SUBSTITUTE(C11, ".", " ")</f>
         <v>Inteligente</v>
       </c>
-      <c r="T11" s="37" t="str">
-        <f t="shared" ref="T11:T12" si="33">SUBSTITUTE(D11, ".", " ")</f>
+      <c r="U11" s="37" t="str">
+        <f t="shared" ref="U11:U12" si="31">SUBSTITUTE(D11, ".", " ")</f>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="U11" s="37" t="str">
-        <f t="shared" ref="U11:U12" si="34">SUBSTITUTE(E11, ".", " ")</f>
+      <c r="V11" s="37" t="str">
+        <f t="shared" ref="V11:V12" si="32">SUBSTITUTE(E11, ".", " ")</f>
         <v>Linguagens</v>
       </c>
-      <c r="V11" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W11" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W11" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X11" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-11</v>
       </c>
-      <c r="X11" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y11" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z11" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA11" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a computer language used to automate project tasks.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA11" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB11" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC11" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="33">
         <v>12</v>
       </c>
       <c r="B12" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="F12" s="35" t="s">
-        <v>150</v>
-      </c>
       <c r="G12" s="58" t="s">
         <v>10</v>
       </c>
@@ -3103,82 +3232,86 @@
         <v>10</v>
       </c>
       <c r="L12" s="36" t="str">
+        <f t="shared" si="26"/>
+        <v>Inteligente</v>
+      </c>
+      <c r="M12" s="36" t="str">
+        <f t="shared" si="27"/>
+        <v>Agêntica.Artificial</v>
+      </c>
+      <c r="N12" s="36" t="str">
         <f t="shared" si="28"/>
+        <v>Linguagens</v>
+      </c>
+      <c r="O12" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v>Sintaxe</v>
+      </c>
+      <c r="P12" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q12" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="R12" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="S12" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T12" s="37" t="str">
+        <f t="shared" si="30"/>
         <v>Inteligente</v>
       </c>
-      <c r="M12" s="36" t="str">
-        <f t="shared" si="29"/>
-        <v>Agêntica.Artificial</v>
-      </c>
-      <c r="N12" s="36" t="str">
-        <f t="shared" si="30"/>
+      <c r="U12" s="37" t="str">
+        <f t="shared" si="31"/>
+        <v>Agêntica Artificial</v>
+      </c>
+      <c r="V12" s="37" t="str">
+        <f t="shared" si="32"/>
         <v>Linguagens</v>
       </c>
-      <c r="O12" s="36" t="str">
-        <f t="shared" si="31"/>
-        <v>Sintaxe</v>
-      </c>
-      <c r="P12" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q12" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara una sintaxis artificial usada para automatizar tareas del proyecto.</v>
-      </c>
-      <c r="R12" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S12" s="37" t="str">
-        <f t="shared" si="32"/>
-        <v>Inteligente</v>
-      </c>
-      <c r="T12" s="37" t="str">
-        <f t="shared" si="33"/>
-        <v>Agêntica Artificial</v>
-      </c>
-      <c r="U12" s="37" t="str">
-        <f t="shared" si="34"/>
-        <v>Linguagens</v>
-      </c>
-      <c r="V12" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W12" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W12" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X12" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-12</v>
       </c>
-      <c r="X12" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y12" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z12" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA12" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares an artificial syntax used to automate project tasks.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+      <c r="AA12" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB12" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC12" s="37" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="33">
         <v>13</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>10</v>
@@ -3196,96 +3329,100 @@
         <v>10</v>
       </c>
       <c r="L13" s="36" t="str">
-        <f t="shared" ref="L13" si="35">CONCATENATE("", C13)</f>
+        <f t="shared" ref="L13" si="33">CONCATENATE("", C13)</f>
         <v>Inteligente</v>
       </c>
       <c r="M13" s="36" t="str">
-        <f t="shared" ref="M13" si="36">CONCATENATE("", D13)</f>
+        <f t="shared" ref="M13" si="34">CONCATENATE("", D13)</f>
         <v>Agêntica.Artificial</v>
       </c>
       <c r="N13" s="36" t="str">
-        <f t="shared" ref="N13" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N13" si="35">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
         <v>Linguagens</v>
       </c>
       <c r="O13" s="36" t="str">
-        <f t="shared" ref="O13" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F13),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O13" si="36">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F13),"."," ")," De "," de "))</f>
         <v>Semântico</v>
       </c>
       <c r="P13" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q13" s="37" t="str">
-        <f t="shared" si="3"/>
-        <v>Declara una semántica específica usada para dar significado a los elementos del proyecto.</v>
+        <v>178</v>
+      </c>
+      <c r="Q13" s="37" t="s">
+        <v>218</v>
       </c>
       <c r="R13" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" s="37" t="str">
-        <f t="shared" ref="S13" si="39">SUBSTITUTE(C13, ".", " ")</f>
+        <v>206</v>
+      </c>
+      <c r="S13" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T13" s="37" t="str">
+        <f t="shared" ref="T13" si="37">SUBSTITUTE(C13, ".", " ")</f>
         <v>Inteligente</v>
       </c>
-      <c r="T13" s="37" t="str">
-        <f t="shared" ref="T13" si="40">SUBSTITUTE(D13, ".", " ")</f>
+      <c r="U13" s="37" t="str">
+        <f t="shared" ref="U13" si="38">SUBSTITUTE(D13, ".", " ")</f>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="U13" s="37" t="str">
-        <f t="shared" ref="U13" si="41">SUBSTITUTE(E13, ".", " ")</f>
+      <c r="V13" s="37" t="str">
+        <f t="shared" ref="V13" si="39">SUBSTITUTE(E13, ".", " ")</f>
         <v>Linguagens</v>
       </c>
-      <c r="V13" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="W13" s="52" t="str">
-        <f t="shared" si="5"/>
+      <c r="W13" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X13" s="52" t="str">
+        <f t="shared" si="4"/>
         <v>Key-AGEN-13</v>
       </c>
-      <c r="X13" s="37" t="s">
-        <v>10</v>
-      </c>
       <c r="Y13" s="37" t="s">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="Z13" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA13" s="37" t="str">
-        <f t="shared" si="11"/>
-        <v>Declares a specific semantics used to give meaning to the elements of the project.</v>
+        <v>223</v>
+      </c>
+      <c r="AA13" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AB13" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="AC13" s="37" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B13">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6 L3:O6 AB3:XFD6">
-    <cfRule type="cellIs" dxfId="13" priority="78" operator="equal">
+  <conditionalFormatting sqref="F2:F6 L3:O6 AD3:XFD6">
+    <cfRule type="cellIs" dxfId="13" priority="79" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="12" priority="633"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="665"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="667"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="668"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="676"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F13">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F1048576 F1:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA13">
-    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
+  <conditionalFormatting sqref="R1:R13">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3298,15 +3435,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -3371,7 +3508,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3446,16 +3583,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" customWidth="1"/>
+    <col min="3" max="3" width="10.69140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3046875" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3472,7 +3609,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -3503,36 +3640,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="42" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="40" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" style="40" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="40" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="40" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" style="40" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.85546875" style="40" customWidth="1"/>
-    <col min="10" max="10" width="5.85546875" style="40" customWidth="1"/>
-    <col min="11" max="12" width="9.7109375" style="40" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="40" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="40" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" style="40" customWidth="1"/>
-    <col min="16" max="16" width="3.5703125" style="40" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="42" customWidth="1"/>
+    <col min="3" max="3" width="5.53515625" style="40" customWidth="1"/>
+    <col min="4" max="4" width="5.84375" style="40" customWidth="1"/>
+    <col min="5" max="5" width="5.3828125" style="40" customWidth="1"/>
+    <col min="6" max="6" width="5.53515625" style="40" customWidth="1"/>
+    <col min="7" max="7" width="6.3828125" style="40" customWidth="1"/>
+    <col min="8" max="8" width="3.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.84375" style="40" customWidth="1"/>
+    <col min="10" max="10" width="5.84375" style="40" customWidth="1"/>
+    <col min="11" max="12" width="9.69140625" style="40" customWidth="1"/>
+    <col min="13" max="13" width="9.15234375" style="40" customWidth="1"/>
+    <col min="14" max="14" width="8.3046875" style="40" customWidth="1"/>
+    <col min="15" max="15" width="13.69140625" style="40" customWidth="1"/>
+    <col min="16" max="16" width="3.53515625" style="40" customWidth="1"/>
     <col min="17" max="17" width="9" style="40" customWidth="1"/>
-    <col min="18" max="18" width="5.140625" style="40" customWidth="1"/>
-    <col min="19" max="19" width="47.5703125" style="40" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" style="54" customWidth="1"/>
+    <col min="18" max="18" width="5.15234375" style="40" customWidth="1"/>
+    <col min="19" max="19" width="47.53515625" style="40" customWidth="1"/>
+    <col min="20" max="20" width="7.15234375" style="54" customWidth="1"/>
     <col min="21" max="21" width="39" style="54" customWidth="1"/>
-    <col min="22" max="22" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="54" customWidth="1"/>
-    <col min="24" max="24" width="5.7109375" style="54" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" style="50" customWidth="1"/>
-    <col min="26" max="16384" width="9.28515625" style="40"/>
+    <col min="22" max="22" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.53515625" style="54" customWidth="1"/>
+    <col min="24" max="24" width="5.69140625" style="54" customWidth="1"/>
+    <col min="25" max="25" width="7.3828125" style="50" customWidth="1"/>
+    <col min="26" max="16384" width="9.3046875" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="48" t="s">
         <v>11</v>
       </c>
@@ -3590,30 +3727,30 @@
         <v>75</v>
       </c>
       <c r="U1" s="60" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="V1" s="61" t="s">
         <v>75</v>
       </c>
       <c r="W1" s="60" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="X1" s="61" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="60" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="49">
         <v>2</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D2" s="39" t="s">
         <v>10</v>
@@ -3631,19 +3768,19 @@
         <v>77</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J2" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K2" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="L2" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="L2" s="29" t="s">
-        <v>155</v>
-      </c>
       <c r="M2" s="23" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>10</v>
@@ -3652,63 +3789,63 @@
         <v>10</v>
       </c>
       <c r="P2" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q2" s="23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R2" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S2" s="23" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T2" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="U2" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="V2" s="63" t="s">
         <v>159</v>
       </c>
-      <c r="U2" s="64" t="s">
+      <c r="W2" s="65" t="s">
         <v>160</v>
       </c>
-      <c r="V2" s="63" t="s">
+      <c r="X2" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="W2" s="65" t="s">
+      <c r="Y2" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="X2" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y2" s="66" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="49">
         <v>3</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D3" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F3" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H3" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>10</v>
@@ -3738,7 +3875,7 @@
         <v>76</v>
       </c>
       <c r="S3" s="23" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T3" s="62" t="s">
         <v>10</v>
@@ -3753,39 +3890,39 @@
         <v>10</v>
       </c>
       <c r="X3" s="63" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="Y3" s="66" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="49">
         <v>4</v>
       </c>
       <c r="B4" s="41" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F4" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G4" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H4" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>10</v>
@@ -3815,84 +3952,84 @@
         <v>76</v>
       </c>
       <c r="S4" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="T4" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V4" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X4" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y4" s="66" t="s">
         <v>186</v>
       </c>
-      <c r="T4" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V4" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X4" s="63" t="s">
-        <v>163</v>
-      </c>
-      <c r="Y4" s="66" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="49">
         <v>5</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F5" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G5" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H5" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J5" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K5" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L5" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M5" s="23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N5" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="P5" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q5" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R5" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S5" s="23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T5" s="62" t="s">
         <v>10</v>
@@ -3913,63 +4050,63 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="49">
         <v>6</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F6" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G6" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H6" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M6" s="23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R6" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="T6" s="62" t="s">
         <v>10</v>
@@ -3990,63 +4127,63 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="49">
         <v>7</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D7" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F7" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H7" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M7" s="23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R7" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="T7" s="62" t="s">
         <v>10</v>
@@ -4067,63 +4204,63 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="49">
         <v>8</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F8" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H8" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I8" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="J8" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>109</v>
-      </c>
       <c r="L8" s="29" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M8" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="N8" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="P8" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R8" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T8" s="62" t="s">
         <v>10</v>
@@ -4144,63 +4281,63 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="49">
         <v>9</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D9" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F9" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G9" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H9" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I9" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="J9" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="K9" s="23" t="s">
+      <c r="L9" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="L9" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="N9" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="O9" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>112</v>
-      </c>
       <c r="Q9" s="23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R9" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="T9" s="62" t="s">
         <v>10</v>
@@ -4221,40 +4358,40 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="49">
         <v>10</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F10" s="56" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H10" s="29" t="s">
         <v>77</v>
       </c>
       <c r="I10" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="J10" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>117</v>
-      </c>
       <c r="L10" s="29" t="s">
         <v>10</v>
       </c>
@@ -4262,22 +4399,22 @@
         <v>10</v>
       </c>
       <c r="N10" s="29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="P10" s="29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R10" s="29" t="s">
         <v>76</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="T10" s="62" t="s">
         <v>10</v>

--- a/Versão5/PRO/Ontologia_Agentes.xlsx
+++ b/Versão5/PRO/Ontologia_Agentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AC9D191-447E-4DBA-B1F9-DCDFA4DDB550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F7F099-51CA-4530-BBC6-E62E3F333D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="253">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -742,7 +742,94 @@
     <t>Atributo IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
@@ -833,7 +920,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -948,6 +1035,48 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1048,7 +1177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1233,20 +1362,152 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1262,6 +1523,24 @@
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1798,15 +2077,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="54" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.3046875" style="54"/>
+    <col min="1" max="1" width="9.28515625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.28515625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>46</v>
       </c>
@@ -1817,7 +2096,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
@@ -1828,7 +2107,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>50</v>
       </c>
@@ -1839,7 +2118,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>51</v>
       </c>
@@ -1850,7 +2129,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>52</v>
       </c>
@@ -1862,7 +2141,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
@@ -1874,7 +2153,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>54</v>
       </c>
@@ -1885,7 +2164,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
@@ -1896,7 +2175,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>57</v>
       </c>
@@ -1907,7 +2186,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>59</v>
       </c>
@@ -1918,7 +2197,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>61</v>
       </c>
@@ -1929,7 +2208,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>62</v>
       </c>
@@ -1940,7 +2219,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>63</v>
       </c>
@@ -1951,7 +2230,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>64</v>
       </c>
@@ -1962,7 +2241,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>65</v>
       </c>
@@ -1973,7 +2252,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>66</v>
       </c>
@@ -1984,7 +2263,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>67</v>
       </c>
@@ -1995,19 +2274,19 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="20">
         <f ca="1">NOW()</f>
-        <v>46253.798913078703</v>
+        <v>46259.702311342589</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>88</v>
       </c>
@@ -2018,7 +2297,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>89</v>
       </c>
@@ -2030,7 +2309,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>90</v>
       </c>
@@ -2042,7 +2321,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
@@ -2053,7 +2332,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>70</v>
       </c>
@@ -2064,7 +2343,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>71</v>
       </c>
@@ -2075,7 +2354,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>72</v>
       </c>
@@ -2087,7 +2366,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>83</v>
       </c>
@@ -2107,38 +2386,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC13"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.61328125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.4609375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.61328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.23046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.61328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.4609375" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.07421875" style="13" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.5703125" style="13" customWidth="1"/>
+    <col min="22" max="22" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="13" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" style="53" customWidth="1"/>
     <col min="25" max="25" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="32" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.3828125" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.7109375" style="32" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.42578125" style="32" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="31" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="3" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="2"/>
+    <col min="29" max="29" width="5" style="31" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="28" customFormat="1" ht="39.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" s="28" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26">
         <v>0</v>
       </c>
@@ -2227,7 +2506,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -2305,26 +2584,26 @@
         <v>142</v>
       </c>
       <c r="X2" s="52" t="str">
-        <f t="shared" ref="X2:X13" si="4">CONCATENATE("Key-AGEN-",A2)</f>
+        <f t="shared" ref="X2:X14" si="4">CONCATENATE("Key-AGEN-",A2)</f>
         <v>Key-AGEN-2</v>
       </c>
-      <c r="Y2" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z2" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA2" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB2" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC2" s="37" t="s">
-        <v>223</v>
+      <c r="Y2" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z2" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA2" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB2" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2405,23 +2684,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-3</v>
       </c>
-      <c r="Y3" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z3" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA3" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB3" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC3" s="37" t="s">
-        <v>223</v>
+      <c r="Y3" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2502,23 +2781,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-4</v>
       </c>
-      <c r="Y4" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z4" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA4" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB4" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC4" s="37" t="s">
-        <v>223</v>
+      <c r="Y4" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2599,23 +2878,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-5</v>
       </c>
-      <c r="Y5" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z5" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA5" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB5" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC5" s="37" t="s">
-        <v>223</v>
+      <c r="Y5" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2696,23 +2975,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-6</v>
       </c>
-      <c r="Y6" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z6" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA6" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB6" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC6" s="37" t="s">
-        <v>223</v>
+      <c r="Y6" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>7</v>
       </c>
@@ -2793,23 +3072,23 @@
         <f t="shared" ref="X7" si="21">CONCATENATE("Key-AGEN-",A7)</f>
         <v>Key-AGEN-7</v>
       </c>
-      <c r="Y7" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z7" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA7" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB7" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC7" s="37" t="s">
-        <v>223</v>
+      <c r="Y7" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -2890,23 +3169,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-8</v>
       </c>
-      <c r="Y8" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z8" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA8" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB8" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC8" s="37" t="s">
-        <v>223</v>
+      <c r="Y8" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -2987,23 +3266,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-9</v>
       </c>
-      <c r="Y9" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z9" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA9" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB9" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC9" s="37" t="s">
-        <v>223</v>
+      <c r="Y9" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC9" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -3084,23 +3363,23 @@
         <f t="shared" ref="X10" si="25">CONCATENATE("Key-AGEN-",A10)</f>
         <v>Key-AGEN-10</v>
       </c>
-      <c r="Y10" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z10" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA10" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB10" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC10" s="37" t="s">
-        <v>223</v>
+      <c r="Y10" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -3181,23 +3460,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-11</v>
       </c>
-      <c r="Y11" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z11" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA11" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB11" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC11" s="37" t="s">
-        <v>223</v>
+      <c r="Y11" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>12</v>
       </c>
@@ -3278,23 +3557,23 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-12</v>
       </c>
-      <c r="Y12" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z12" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA12" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB12" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC12" s="37" t="s">
-        <v>223</v>
+      <c r="Y12" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB12" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>13</v>
       </c>
@@ -3357,7 +3636,7 @@
         <v>10</v>
       </c>
       <c r="T13" s="37" t="str">
-        <f t="shared" ref="T13" si="37">SUBSTITUTE(C13, ".", " ")</f>
+        <f t="shared" ref="T13:V14" si="37">SUBSTITUTE(C13, ".", " ")</f>
         <v>Inteligente</v>
       </c>
       <c r="U13" s="37" t="str">
@@ -3375,54 +3654,164 @@
         <f t="shared" si="4"/>
         <v>Key-AGEN-13</v>
       </c>
-      <c r="Y13" s="37" t="s">
+      <c r="Y13" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB13" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="33">
+        <v>14</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="66" t="s">
         <v>223</v>
       </c>
-      <c r="Z13" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA13" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AB13" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC13" s="37" t="s">
-        <v>223</v>
+      <c r="D14" s="66" t="s">
+        <v>224</v>
+      </c>
+      <c r="E14" s="66" t="s">
+        <v>225</v>
+      </c>
+      <c r="F14" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="G14" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="36" t="str">
+        <f t="shared" ref="L14:O14" si="40">SUBSTITUTE(CONCATENATE("", C14), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M14" s="36" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N14" s="36" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="O14" s="36" t="str">
+        <f t="shared" si="40"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P14" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q14" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="R14" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="S14" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="37" t="str">
+        <f t="shared" si="37"/>
+        <v>De API</v>
+      </c>
+      <c r="U14" s="37" t="str">
+        <f t="shared" si="37"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V14" s="38" t="str">
+        <f t="shared" si="37"/>
+        <v>Macros</v>
+      </c>
+      <c r="W14" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="X14" s="52" t="str">
+        <f t="shared" si="4"/>
+        <v>Key-AGEN-14</v>
+      </c>
+      <c r="Y14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="64" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B13">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
+  <conditionalFormatting sqref="A2:B9 B10:B13 A10:A14">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
+  <conditionalFormatting sqref="F1:F13 F15:F1048576">
+    <cfRule type="duplicateValues" dxfId="27" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6 L3:O6 AD3:XFD6">
-    <cfRule type="cellIs" dxfId="13" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="12" priority="634"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="667"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="668"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F13">
-    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F1048576 F1:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="22"/>
+  <conditionalFormatting sqref="F15:F1048576 F1:F6">
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R13">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R14">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3435,15 +3824,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -3508,7 +3897,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3583,16 +3972,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3609,7 +3998,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -3628,7 +4017,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3639,37 +4028,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AO15"/>
+  <sheetFormatPr defaultColWidth="4.85546875" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="42" customWidth="1"/>
-    <col min="3" max="3" width="5.53515625" style="40" customWidth="1"/>
-    <col min="4" max="4" width="5.84375" style="40" customWidth="1"/>
-    <col min="5" max="5" width="5.3828125" style="40" customWidth="1"/>
-    <col min="6" max="6" width="5.53515625" style="40" customWidth="1"/>
-    <col min="7" max="7" width="6.3828125" style="40" customWidth="1"/>
-    <col min="8" max="8" width="3.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.84375" style="40" customWidth="1"/>
-    <col min="10" max="10" width="5.84375" style="40" customWidth="1"/>
-    <col min="11" max="12" width="9.69140625" style="40" customWidth="1"/>
-    <col min="13" max="13" width="9.15234375" style="40" customWidth="1"/>
-    <col min="14" max="14" width="8.3046875" style="40" customWidth="1"/>
-    <col min="15" max="15" width="13.69140625" style="40" customWidth="1"/>
-    <col min="16" max="16" width="3.53515625" style="40" customWidth="1"/>
-    <col min="17" max="17" width="9" style="40" customWidth="1"/>
-    <col min="18" max="18" width="5.15234375" style="40" customWidth="1"/>
-    <col min="19" max="19" width="47.53515625" style="40" customWidth="1"/>
-    <col min="20" max="20" width="7.15234375" style="54" customWidth="1"/>
-    <col min="21" max="21" width="39" style="54" customWidth="1"/>
-    <col min="22" max="22" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.53515625" style="54" customWidth="1"/>
-    <col min="24" max="24" width="5.69140625" style="54" customWidth="1"/>
-    <col min="25" max="25" width="7.3828125" style="50" customWidth="1"/>
-    <col min="26" max="16384" width="9.3046875" style="40"/>
+    <col min="1" max="1" width="2.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" style="40" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" style="40" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" style="40" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" style="40" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="40" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="40" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="40" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" style="40" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" style="40" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="40" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4" style="40" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7109375" style="40" customWidth="1"/>
+    <col min="22" max="22" width="6.140625" style="40" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="40" customWidth="1"/>
+    <col min="24" max="24" width="6" style="40" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.42578125" style="40" customWidth="1"/>
+    <col min="26" max="26" width="7.42578125" style="54" customWidth="1"/>
+    <col min="27" max="27" width="39.7109375" style="54" customWidth="1"/>
+    <col min="28" max="28" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" style="54" customWidth="1"/>
+    <col min="30" max="30" width="7.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" style="40" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="4.85546875" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:41" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="48" t="s">
         <v>11</v>
       </c>
@@ -3726,23 +4132,71 @@
       <c r="T1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="U1" s="60" t="s">
+      <c r="U1" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="W1" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="X1" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA1" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="V1" s="61" t="s">
+      <c r="AB1" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="W1" s="60" t="s">
+      <c r="AC1" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="X1" s="61" t="s">
+      <c r="AD1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="Y1" s="60" t="s">
+      <c r="AE1" s="79" t="s">
         <v>156</v>
       </c>
+      <c r="AF1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG1" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI1" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="AJ1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK1" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="AL1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="AM1" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN1" s="61" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO1" s="60" t="s">
+        <v>156</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -3755,7 +4209,7 @@
       <c r="D2" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="80" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="29" t="s">
@@ -3795,31 +4249,79 @@
         <v>163</v>
       </c>
       <c r="R2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="23" t="s">
+      <c r="Y2" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="T2" s="63" t="s">
+      <c r="Z2" s="62" t="s">
         <v>157</v>
       </c>
-      <c r="U2" s="64" t="s">
+      <c r="AA2" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="V2" s="63" t="s">
+      <c r="AB2" s="62" t="s">
         <v>159</v>
       </c>
-      <c r="W2" s="65" t="s">
+      <c r="AC2" s="76" t="s">
         <v>160</v>
       </c>
-      <c r="X2" s="63" t="s">
+      <c r="AD2" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="Y2" s="66" t="s">
+      <c r="AE2" s="23" t="s">
         <v>162</v>
       </c>
+      <c r="AF2" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG2" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH2" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK2" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL2" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM2" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN2" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO2" s="68" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -3832,7 +4334,7 @@
       <c r="D3" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F3" s="56" t="s">
@@ -3872,31 +4374,79 @@
         <v>10</v>
       </c>
       <c r="R3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V3" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S3" s="23" t="s">
+      <c r="Y3" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="T3" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V3" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X3" s="63" t="s">
+      <c r="Z3" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="Y3" s="66" t="s">
+      <c r="AE3" s="23" t="s">
         <v>185</v>
       </c>
+      <c r="AF3" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="68" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -3909,7 +4459,7 @@
       <c r="D4" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F4" s="56" t="s">
@@ -3949,31 +4499,79 @@
         <v>10</v>
       </c>
       <c r="R4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S4" s="23" t="s">
+      <c r="Y4" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="T4" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V4" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X4" s="63" t="s">
+      <c r="Z4" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="63" t="s">
         <v>161</v>
       </c>
-      <c r="Y4" s="66" t="s">
+      <c r="AE4" s="23" t="s">
         <v>186</v>
       </c>
+      <c r="AF4" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH4" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ4" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL4" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM4" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN4" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="68" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -3986,7 +4584,7 @@
       <c r="D5" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F5" s="56" t="s">
@@ -4026,31 +4624,79 @@
         <v>117</v>
       </c>
       <c r="R5" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V5" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X5" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S5" s="23" t="s">
+      <c r="Y5" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="T5" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V5" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X5" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y5" s="66" t="s">
+      <c r="Z5" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF5" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG5" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH5" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI5" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ5" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK5" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL5" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM5" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN5" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO5" s="68" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -4063,7 +4709,7 @@
       <c r="D6" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F6" s="56" t="s">
@@ -4103,31 +4749,79 @@
         <v>117</v>
       </c>
       <c r="R6" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T6" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V6" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X6" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S6" s="23" t="s">
+      <c r="Y6" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="T6" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V6" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X6" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y6" s="66" t="s">
+      <c r="Z6" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD6" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF6" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG6" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH6" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI6" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ6" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK6" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL6" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM6" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN6" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO6" s="68" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -4140,7 +4834,7 @@
       <c r="D7" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F7" s="56" t="s">
@@ -4180,31 +4874,79 @@
         <v>117</v>
       </c>
       <c r="R7" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V7" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X7" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S7" s="23" t="s">
+      <c r="Y7" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="T7" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V7" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X7" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y7" s="66" t="s">
+      <c r="Z7" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD7" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF7" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG7" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH7" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI7" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ7" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK7" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL7" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM7" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN7" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO7" s="68" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -4217,7 +4959,7 @@
       <c r="D8" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F8" s="56" t="s">
@@ -4257,31 +4999,79 @@
         <v>116</v>
       </c>
       <c r="R8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V8" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X8" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S8" s="23" t="s">
+      <c r="Y8" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="T8" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V8" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X8" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y8" s="66" t="s">
+      <c r="Z8" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG8" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI8" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK8" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM8" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN8" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO8" s="68" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -4294,7 +5084,7 @@
       <c r="D9" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F9" s="56" t="s">
@@ -4334,31 +5124,79 @@
         <v>111</v>
       </c>
       <c r="R9" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V9" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S9" s="23" t="s">
+      <c r="Y9" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="T9" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V9" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X9" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y9" s="66" t="s">
+      <c r="Z9" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC9" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE9" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF9" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG9" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH9" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI9" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ9" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK9" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL9" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM9" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN9" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO9" s="68" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -4371,7 +5209,7 @@
       <c r="D10" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="80" t="s">
         <v>149</v>
       </c>
       <c r="F10" s="56" t="s">
@@ -4411,33 +5249,755 @@
         <v>114</v>
       </c>
       <c r="R10" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T10" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V10" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X10" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="S10" s="23" t="s">
+      <c r="Y10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="T10" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="U10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V10" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="W10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X10" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="Y10" s="66" t="s">
+      <c r="Z10" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF10" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG10" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH10" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI10" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ10" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK10" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL10" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM10" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN10" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO10" s="68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="49">
+        <v>11</v>
+      </c>
+      <c r="B11" s="73" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R11" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="S11" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="T11" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="U11" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="V11" s="70" t="str">
+        <f t="shared" ref="V11:V15" si="0">IF(W11="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="W11" s="71" t="s">
+        <v>236</v>
+      </c>
+      <c r="X11" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z11" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF11" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG11" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH11" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI11" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ11" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK11" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL11" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM11" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN11" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO11" s="68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="49">
+        <v>12</v>
+      </c>
+      <c r="B12" s="73" t="s">
+        <v>237</v>
+      </c>
+      <c r="C12" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R12" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="S12" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="T12" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="U12" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="V12" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="W12" s="71" t="s">
+        <v>240</v>
+      </c>
+      <c r="X12" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y12" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z12" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB12" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF12" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG12" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH12" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI12" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ12" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK12" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL12" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM12" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN12" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO12" s="68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="49">
+        <v>13</v>
+      </c>
+      <c r="B13" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="C13" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P13" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R13" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="S13" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="T13" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="U13" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="V13" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="W13" s="71" t="s">
+        <v>244</v>
+      </c>
+      <c r="X13" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y13" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z13" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB13" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD13" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG13" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI13" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK13" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM13" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO13" s="68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="49">
+        <v>14</v>
+      </c>
+      <c r="B14" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R14" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="S14" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="T14" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="U14" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="V14" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="W14" s="71" t="s">
+        <v>248</v>
+      </c>
+      <c r="X14" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y14" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z14" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM14" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="49">
+        <v>15</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="S15" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="T15" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="U15" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="V15" s="70" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="W15" s="71" t="s">
+        <v>252</v>
+      </c>
+      <c r="X15" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y15" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z15" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA15" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE15" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF15" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG15" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH15" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI15" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ15" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK15" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL15" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM15" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN15" s="67" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO15" s="68" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="T1:Y10">
+  <conditionalFormatting sqref="Z1:AE10 AD11:AE15">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B15">
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z11:AC15">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AM15">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN2:AO15">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF1:AG1">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH1:AI1">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AJ1:AK1">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL1:AM1">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN1:AO1">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>

--- a/Versão5/PRO/Ontologia_Agentes.xlsx
+++ b/Versão5/PRO/Ontologia_Agentes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F7F099-51CA-4530-BBC6-E62E3F333D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C24ACB-A4A8-4F79-96AC-2581A7BEA621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1415,71 +1415,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <b val="0"/>
@@ -1513,14 +1449,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -1541,22 +1469,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2077,15 +1989,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="54" customWidth="1"/>
-    <col min="2" max="2" width="51.7109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.28515625" style="54"/>
+    <col min="1" max="1" width="9.3046875" style="54" customWidth="1"/>
+    <col min="2" max="2" width="51.69140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.3046875" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="17" t="s">
         <v>46</v>
       </c>
@@ -2096,7 +2008,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
@@ -2107,7 +2019,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="18" t="s">
         <v>50</v>
       </c>
@@ -2118,7 +2030,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
         <v>51</v>
       </c>
@@ -2129,7 +2041,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
         <v>52</v>
       </c>
@@ -2141,7 +2053,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
@@ -2153,7 +2065,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
         <v>54</v>
       </c>
@@ -2164,7 +2076,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
@@ -2175,7 +2087,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
         <v>57</v>
       </c>
@@ -2186,7 +2098,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
         <v>59</v>
       </c>
@@ -2197,7 +2109,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
         <v>61</v>
       </c>
@@ -2208,7 +2120,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
         <v>62</v>
       </c>
@@ -2219,7 +2131,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
         <v>63</v>
       </c>
@@ -2230,7 +2142,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
         <v>64</v>
       </c>
@@ -2241,7 +2153,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
         <v>65</v>
       </c>
@@ -2252,7 +2164,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>66</v>
       </c>
@@ -2263,7 +2175,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
         <v>67</v>
       </c>
@@ -2274,19 +2186,19 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="20">
         <f ca="1">NOW()</f>
-        <v>46259.702311342589</v>
+        <v>46264.568247916664</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
         <v>88</v>
       </c>
@@ -2297,7 +2209,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
         <v>89</v>
       </c>
@@ -2309,7 +2221,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
         <v>90</v>
       </c>
@@ -2321,7 +2233,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
@@ -2332,7 +2244,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
         <v>70</v>
       </c>
@@ -2343,7 +2255,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
         <v>71</v>
       </c>
@@ -2354,7 +2266,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
         <v>72</v>
       </c>
@@ -2366,7 +2278,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
         <v>83</v>
       </c>
@@ -2387,37 +2299,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5703125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.53515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.69140625" style="13" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.5703125" style="13" customWidth="1"/>
-    <col min="22" max="22" width="7.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="13" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" style="53" customWidth="1"/>
+    <col min="14" max="14" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.69140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.3046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.53515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.53515625" style="13" customWidth="1"/>
+    <col min="22" max="22" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.3046875" style="13" customWidth="1"/>
+    <col min="24" max="24" width="7.3046875" style="53" customWidth="1"/>
     <col min="25" max="25" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.42578125" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.69140625" style="32" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="32" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="31" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5" style="31" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="2"/>
+    <col min="30" max="16384" width="9.15234375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="28" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="28" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="26">
         <v>0</v>
       </c>
@@ -2506,7 +2418,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="33">
         <v>2</v>
       </c>
@@ -2603,7 +2515,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="33">
         <v>3</v>
       </c>
@@ -2700,7 +2612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="33">
         <v>4</v>
       </c>
@@ -2797,7 +2709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="33">
         <v>5</v>
       </c>
@@ -2894,7 +2806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="33">
         <v>6</v>
       </c>
@@ -2991,7 +2903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="33">
         <v>7</v>
       </c>
@@ -3088,7 +3000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="33">
         <v>8</v>
       </c>
@@ -3185,7 +3097,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="33">
         <v>9</v>
       </c>
@@ -3282,7 +3194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="33">
         <v>10</v>
       </c>
@@ -3379,7 +3291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="33">
         <v>11</v>
       </c>
@@ -3476,7 +3388,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="33">
         <v>12</v>
       </c>
@@ -3573,7 +3485,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="33">
         <v>13</v>
       </c>
@@ -3670,7 +3582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>14</v>
       </c>
@@ -3681,10 +3593,10 @@
         <v>223</v>
       </c>
       <c r="D14" s="66" t="s">
+        <v>225</v>
+      </c>
+      <c r="E14" s="66" t="s">
         <v>224</v>
-      </c>
-      <c r="E14" s="66" t="s">
-        <v>225</v>
       </c>
       <c r="F14" s="66" t="s">
         <v>226</v>
@@ -3710,11 +3622,11 @@
       </c>
       <c r="M14" s="36" t="str">
         <f t="shared" si="40"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N14" s="36" t="str">
         <f t="shared" si="40"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O14" s="36" t="str">
         <f t="shared" si="40"/>
@@ -3738,11 +3650,11 @@
       </c>
       <c r="U14" s="37" t="str">
         <f t="shared" si="37"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V14" s="38" t="str">
         <f t="shared" si="37"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W14" s="37" t="s">
         <v>142</v>
@@ -3769,49 +3681,39 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B9 B10:B13 A10:A14">
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B14">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F13 F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6 L3:O6 AD3:XFD6">
-    <cfRule type="cellIs" dxfId="26" priority="82" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="82" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="25" priority="637"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="672"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="673"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F13">
-    <cfRule type="duplicateValues" dxfId="18" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:F1048576 F1:F6">
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R13">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R14">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R14">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3824,15 +3726,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -3897,7 +3799,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3972,16 +3874,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.15234375" customWidth="1"/>
+    <col min="3" max="3" width="10.69140625" customWidth="1"/>
+    <col min="4" max="4" width="8.3046875" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3998,7 +3900,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -4017,7 +3919,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4029,53 +3931,53 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AO15"/>
-  <sheetFormatPr defaultColWidth="4.85546875" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="4.84375" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="40" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.84375" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.84375" style="40" customWidth="1"/>
+    <col min="5" max="5" width="6.3828125" style="40" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="40" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" style="40" customWidth="1"/>
-    <col min="8" max="8" width="3.42578125" style="40" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="40" customWidth="1"/>
-    <col min="10" max="10" width="6.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.84375" style="40" customWidth="1"/>
+    <col min="8" max="8" width="3.3828125" style="40" customWidth="1"/>
+    <col min="9" max="9" width="8.69140625" style="40" customWidth="1"/>
+    <col min="10" max="10" width="6.53515625" style="40" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="40" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" style="40" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" style="40" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" style="40" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" style="40" customWidth="1"/>
-    <col min="18" max="18" width="6.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.3828125" style="40" customWidth="1"/>
+    <col min="13" max="13" width="11.15234375" style="40" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.15234375" style="40" customWidth="1"/>
+    <col min="15" max="15" width="13.69140625" style="40" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.3828125" style="40" customWidth="1"/>
+    <col min="18" max="18" width="6.53515625" style="40" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="4" style="40" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.7109375" style="40" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" style="40" customWidth="1"/>
-    <col min="23" max="23" width="8.5703125" style="40" customWidth="1"/>
+    <col min="20" max="20" width="5.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.69140625" style="40" customWidth="1"/>
+    <col min="22" max="22" width="6.15234375" style="40" customWidth="1"/>
+    <col min="23" max="23" width="8.53515625" style="40" customWidth="1"/>
     <col min="24" max="24" width="6" style="40" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="48.42578125" style="40" customWidth="1"/>
-    <col min="26" max="26" width="7.42578125" style="54" customWidth="1"/>
-    <col min="27" max="27" width="39.7109375" style="54" customWidth="1"/>
-    <col min="28" max="28" width="5.7109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.3828125" style="40" customWidth="1"/>
+    <col min="26" max="26" width="7.3828125" style="54" customWidth="1"/>
+    <col min="27" max="27" width="39.69140625" style="54" customWidth="1"/>
+    <col min="28" max="28" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="15" style="54" customWidth="1"/>
-    <col min="30" max="30" width="7.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.7109375" style="40" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="4.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="4.85546875" style="40"/>
+    <col min="30" max="30" width="7.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.69140625" style="40" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="4.84375" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="48" t="s">
         <v>11</v>
       </c>
@@ -4196,7 +4098,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="49">
         <v>2</v>
       </c>
@@ -4321,7 +4223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="49">
         <v>3</v>
       </c>
@@ -4446,7 +4348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="49">
         <v>4</v>
       </c>
@@ -4571,7 +4473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="49">
         <v>5</v>
       </c>
@@ -4696,7 +4598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="49">
         <v>6</v>
       </c>
@@ -4821,7 +4723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="49">
         <v>7</v>
       </c>
@@ -4946,7 +4848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="49">
         <v>8</v>
       </c>
@@ -5071,7 +4973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="49">
         <v>9</v>
       </c>
@@ -5196,7 +5098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="49">
         <v>10</v>
       </c>
@@ -5321,7 +5223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="49">
         <v>11</v>
       </c>
@@ -5447,7 +5349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="49">
         <v>12</v>
       </c>
@@ -5573,7 +5475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="49">
         <v>13</v>
       </c>
@@ -5699,7 +5601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>14</v>
       </c>
@@ -5825,7 +5727,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="49">
         <v>15</v>
       </c>
@@ -5953,51 +5855,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="Z1:AE10 AD11:AE15">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B11:B15">
+    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:B15">
-    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z11:AC15">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AM15">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AO15">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF1:AG1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH1:AI1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AJ1:AK1">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL1:AM1">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN1:AO1">
+  <conditionalFormatting sqref="Z1:AO15">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>

--- a/Versão5/PRO/Ontologia_Agentes.xlsx
+++ b/Versão5/PRO/Ontologia_Agentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C24ACB-A4A8-4F79-96AC-2581A7BEA621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CD23A0-EFC5-4C40-A789-5A6F9FB5848A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="271">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -751,18 +751,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -830,6 +818,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -920,7 +974,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1077,6 +1131,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1177,7 +1237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1273,9 +1333,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1367,9 +1424,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1410,12 +1464,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
     <dxf>
       <font>
         <b val="0"/>
@@ -1567,6 +1630,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1989,59 +2062,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" style="54" customWidth="1"/>
-    <col min="2" max="2" width="51.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.3046875" style="54"/>
+    <col min="1" max="1" width="9.28515625" style="53" customWidth="1"/>
+    <col min="2" max="2" width="51.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.28515625" style="53"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>46</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="43" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>48</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>50</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>51</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>52</v>
       </c>
@@ -2049,11 +2122,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="45" t="s">
+      <c r="C5" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>53</v>
       </c>
@@ -2061,155 +2134,155 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C6" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>54</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C7" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>56</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>59</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>61</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C13" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>64</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>65</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>66</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>67</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>68</v>
       </c>
       <c r="B18" s="20">
         <f ca="1">NOW()</f>
-        <v>46264.568247916664</v>
-      </c>
-      <c r="C18" s="45" t="s">
+        <v>46268.698605324076</v>
+      </c>
+      <c r="C18" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>88</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C19" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>89</v>
       </c>
@@ -2217,11 +2290,11 @@
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="44" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>90</v>
       </c>
@@ -2229,44 +2302,44 @@
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C21" s="44" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>70</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>71</v>
       </c>
       <c r="B24" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>72</v>
       </c>
@@ -2274,11 +2347,11 @@
         <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formaliza las clases para agentes.</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="C25" s="44" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>83</v>
       </c>
@@ -2286,7 +2359,7 @@
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize agent classes.</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="44" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2298,38 +2371,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC14"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AD18"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3046875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.53515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.3828125" style="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7" style="12" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.69140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.3046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.53515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.69140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.53515625" style="13" customWidth="1"/>
-    <col min="22" max="22" width="7.3828125" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.3046875" style="13" customWidth="1"/>
-    <col min="24" max="24" width="7.3046875" style="53" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="45.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" style="52" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="6" style="32" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.69140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.3828125" style="32" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5703125" style="32" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" style="31" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5" style="31" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="2"/>
+    <col min="29" max="30" width="5.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="28" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" s="28" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26">
         <v>0</v>
       </c>
@@ -2348,19 +2421,19 @@
       <c r="F1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="59" t="s">
+      <c r="K1" s="58" t="s">
         <v>4</v>
       </c>
       <c r="L1" s="16" t="s">
@@ -2381,10 +2454,10 @@
       <c r="Q1" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="R1" s="43" t="s">
+      <c r="R1" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="S1" s="55" t="s">
+      <c r="S1" s="54" t="s">
         <v>40</v>
       </c>
       <c r="T1" s="16" t="s">
@@ -2399,7 +2472,7 @@
       <c r="W1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="50" t="s">
         <v>9</v>
       </c>
       <c r="Y1" s="30" t="s">
@@ -2414,1306 +2487,1751 @@
       <c r="AB1" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="AC1" s="47" t="s">
+      <c r="AC1" s="46" t="s">
         <v>80</v>
       </c>
+      <c r="AD1" s="46" t="s">
+        <v>270</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>2</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="G2" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="36" t="str">
+      <c r="G2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="35" t="str">
         <f t="shared" ref="L2" si="0">CONCATENATE("", C2)</f>
         <v>De.Inteligência.Projetual</v>
       </c>
-      <c r="M2" s="36" t="str">
+      <c r="M2" s="35" t="str">
         <f t="shared" ref="M2" si="1">CONCATENATE("", D2)</f>
         <v>Orquestações</v>
       </c>
-      <c r="N2" s="36" t="str">
+      <c r="N2" s="35" t="str">
         <f t="shared" ref="N2:O2" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
         <v>Agentes Humanos</v>
       </c>
-      <c r="O2" s="36" t="str">
+      <c r="O2" s="35" t="str">
         <f t="shared" si="2"/>
         <v>Agente Humano</v>
       </c>
-      <c r="P2" s="37" t="s">
+      <c r="P2" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="37" t="s">
+      <c r="Q2" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="R2" s="37" t="s">
+      <c r="R2" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="S2" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="T2" s="38" t="str">
+      <c r="S2" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" s="37" t="str">
         <f t="shared" ref="T2:V2" si="3">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="U2" s="38" t="str">
+      <c r="U2" s="37" t="str">
         <f t="shared" si="3"/>
         <v>Orquestações</v>
       </c>
-      <c r="V2" s="38" t="str">
+      <c r="V2" s="37" t="str">
         <f t="shared" si="3"/>
         <v>Agentes Humanos</v>
       </c>
-      <c r="W2" s="37" t="s">
+      <c r="W2" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X2" s="52" t="str">
-        <f t="shared" ref="X2:X14" si="4">CONCATENATE("Key-AGEN-",A2)</f>
+      <c r="X2" s="51" t="str">
+        <f t="shared" ref="X2:X9" si="4">CONCATENATE("Key-AGEN-",A2)</f>
         <v>Key-AGEN-2</v>
       </c>
-      <c r="Y2" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z2" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA2" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB2" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="64" t="s">
+      <c r="Y2" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z2" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA2" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB2" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD2" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33">
         <v>3</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K3" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="36" t="str">
+      <c r="G3" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="35" t="str">
         <f t="shared" ref="L3:M5" si="5">CONCATENATE("", C3)</f>
         <v>De.Inteligência.Projetual</v>
       </c>
-      <c r="M3" s="36" t="str">
+      <c r="M3" s="35" t="str">
         <f t="shared" si="5"/>
         <v>Orquestações</v>
       </c>
-      <c r="N3" s="36" t="str">
+      <c r="N3" s="35" t="str">
         <f t="shared" ref="N3:O5" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
         <v>Agentes Artificiais</v>
       </c>
-      <c r="O3" s="36" t="str">
+      <c r="O3" s="35" t="str">
         <f t="shared" si="6"/>
         <v>Agente Artificial</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="P3" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="Q3" s="37" t="s">
+      <c r="Q3" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="R3" s="37" t="s">
+      <c r="R3" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="S3" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="T3" s="38" t="str">
+      <c r="S3" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T3" s="37" t="str">
         <f t="shared" ref="T3:T5" si="7">SUBSTITUTE(C3, ".", " ")</f>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="U3" s="38" t="str">
+      <c r="U3" s="37" t="str">
         <f t="shared" ref="U3:U5" si="8">SUBSTITUTE(D3, ".", " ")</f>
         <v>Orquestações</v>
       </c>
-      <c r="V3" s="38" t="str">
+      <c r="V3" s="37" t="str">
         <f t="shared" ref="V3:V5" si="9">SUBSTITUTE(E3, ".", " ")</f>
         <v>Agentes Artificiais</v>
       </c>
-      <c r="W3" s="37" t="s">
+      <c r="W3" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X3" s="52" t="str">
+      <c r="X3" s="51" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-3</v>
       </c>
-      <c r="Y3" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z3" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB3" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC3" s="64" t="s">
+      <c r="Y3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>4</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="81" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I4" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K4" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L4" s="36" t="str">
+      <c r="G4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="35" t="str">
         <f t="shared" si="5"/>
         <v>De.Inteligência.Projetual</v>
       </c>
-      <c r="M4" s="36" t="str">
+      <c r="M4" s="35" t="str">
         <f t="shared" si="5"/>
         <v>Orquestações</v>
       </c>
-      <c r="N4" s="36" t="str">
+      <c r="N4" s="35" t="str">
         <f t="shared" si="6"/>
         <v>Computacionais</v>
       </c>
-      <c r="O4" s="36" t="str">
+      <c r="O4" s="35" t="str">
         <f t="shared" si="6"/>
         <v>Gherkin</v>
       </c>
-      <c r="P4" s="37" t="s">
+      <c r="P4" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="Q4" s="37" t="s">
+      <c r="Q4" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="R4" s="37" t="s">
+      <c r="R4" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="S4" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="T4" s="38" t="str">
+      <c r="S4" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T4" s="37" t="str">
         <f t="shared" si="7"/>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="U4" s="38" t="str">
+      <c r="U4" s="37" t="str">
         <f t="shared" si="8"/>
         <v>Orquestações</v>
       </c>
-      <c r="V4" s="38" t="str">
+      <c r="V4" s="37" t="str">
         <f t="shared" si="9"/>
         <v>Computacionais</v>
       </c>
-      <c r="W4" s="37" t="s">
+      <c r="W4" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X4" s="52" t="str">
+      <c r="X4" s="51" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-4</v>
       </c>
-      <c r="Y4" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z4" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB4" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC4" s="64" t="s">
+      <c r="Y4" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z4" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>5</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="F5" s="35" t="s">
+      <c r="F5" s="81" t="s">
         <v>172</v>
       </c>
-      <c r="G5" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I5" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J5" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="36" t="str">
+      <c r="G5" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="35" t="str">
         <f t="shared" si="5"/>
         <v>De.Inteligência.Projetual</v>
       </c>
-      <c r="M5" s="36" t="str">
+      <c r="M5" s="35" t="str">
         <f t="shared" si="5"/>
         <v>Orquestações</v>
       </c>
-      <c r="N5" s="36" t="str">
+      <c r="N5" s="35" t="str">
         <f t="shared" si="6"/>
         <v>Computacionais</v>
       </c>
-      <c r="O5" s="36" t="str">
+      <c r="O5" s="35" t="str">
         <f t="shared" si="6"/>
         <v>Sintática</v>
       </c>
-      <c r="P5" s="37" t="s">
+      <c r="P5" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="Q5" s="37" t="s">
+      <c r="Q5" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="R5" s="37" t="s">
+      <c r="R5" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="S5" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="T5" s="38" t="str">
+      <c r="S5" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T5" s="37" t="str">
         <f t="shared" si="7"/>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="U5" s="38" t="str">
+      <c r="U5" s="37" t="str">
         <f t="shared" si="8"/>
         <v>Orquestações</v>
       </c>
-      <c r="V5" s="38" t="str">
+      <c r="V5" s="37" t="str">
         <f t="shared" si="9"/>
         <v>Computacionais</v>
       </c>
-      <c r="W5" s="37" t="s">
+      <c r="W5" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X5" s="52" t="str">
+      <c r="X5" s="51" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-5</v>
       </c>
-      <c r="Y5" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z5" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB5" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC5" s="64" t="s">
+      <c r="Y5" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:29" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>6</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D6" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="81" t="s">
         <v>173</v>
       </c>
-      <c r="G6" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K6" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L6" s="36" t="str">
+      <c r="G6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="35" t="str">
         <f t="shared" ref="L6:M10" si="10">CONCATENATE("", C6)</f>
         <v>De.Inteligência.Projetual</v>
       </c>
-      <c r="M6" s="36" t="str">
+      <c r="M6" s="35" t="str">
         <f t="shared" ref="M6:M8" si="11">CONCATENATE("", D6)</f>
         <v>Orquestações</v>
       </c>
-      <c r="N6" s="36" t="str">
+      <c r="N6" s="35" t="str">
         <f t="shared" ref="N6:O10" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E6),"."," ")," De "," de "))</f>
         <v>Computacionais</v>
       </c>
-      <c r="O6" s="36" t="str">
+      <c r="O6" s="35" t="str">
         <f t="shared" ref="O6:O8" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F6),"."," ")," De "," de "))</f>
         <v>Semântica</v>
       </c>
-      <c r="P6" s="37" t="s">
+      <c r="P6" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="Q6" s="37" t="s">
+      <c r="Q6" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="R6" s="37" t="s">
+      <c r="R6" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="S6" s="38" t="s">
-        <v>10</v>
-      </c>
-      <c r="T6" s="38" t="str">
+      <c r="S6" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="T6" s="37" t="str">
         <f t="shared" ref="T6:V10" si="14">SUBSTITUTE(C6, ".", " ")</f>
         <v>De Inteligência Projetual</v>
       </c>
-      <c r="U6" s="38" t="str">
+      <c r="U6" s="37" t="str">
         <f t="shared" ref="U6:U8" si="15">SUBSTITUTE(D6, ".", " ")</f>
         <v>Orquestações</v>
       </c>
-      <c r="V6" s="38" t="str">
+      <c r="V6" s="37" t="str">
         <f t="shared" ref="V6:V8" si="16">SUBSTITUTE(E6, ".", " ")</f>
         <v>Computacionais</v>
       </c>
-      <c r="W6" s="37" t="s">
+      <c r="W6" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X6" s="52" t="str">
+      <c r="X6" s="51" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-6</v>
       </c>
-      <c r="Y6" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z6" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB6" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC6" s="64" t="s">
+      <c r="Y6" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD6" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>7</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="79" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="F7" s="35" t="s">
+      <c r="F7" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="G7" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L7" s="36" t="str">
+      <c r="G7" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="35" t="str">
         <f t="shared" si="10"/>
         <v>Inteligente</v>
       </c>
-      <c r="M7" s="36" t="str">
+      <c r="M7" s="35" t="str">
         <f t="shared" ref="M7" si="17">CONCATENATE("", D7)</f>
         <v>Agêntica.Natural</v>
       </c>
-      <c r="N7" s="36" t="str">
+      <c r="N7" s="35" t="str">
         <f t="shared" si="12"/>
         <v>Humanos</v>
       </c>
-      <c r="O7" s="36" t="str">
+      <c r="O7" s="35" t="str">
         <f t="shared" ref="O7" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
         <v>Projetista</v>
       </c>
-      <c r="P7" s="37" t="s">
+      <c r="P7" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="Q7" s="37" t="s">
+      <c r="Q7" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="R7" s="37" t="s">
+      <c r="R7" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="S7" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T7" s="37" t="str">
+      <c r="S7" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T7" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Inteligente</v>
       </c>
-      <c r="U7" s="37" t="str">
+      <c r="U7" s="36" t="str">
         <f t="shared" ref="U7" si="19">SUBSTITUTE(D7, ".", " ")</f>
         <v>Agêntica Natural</v>
       </c>
-      <c r="V7" s="37" t="str">
+      <c r="V7" s="36" t="str">
         <f t="shared" ref="V7" si="20">SUBSTITUTE(E7, ".", " ")</f>
         <v>Humanos</v>
       </c>
-      <c r="W7" s="37" t="s">
+      <c r="W7" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X7" s="52" t="str">
+      <c r="X7" s="51" t="str">
         <f t="shared" ref="X7" si="21">CONCATENATE("Key-AGEN-",A7)</f>
         <v>Key-AGEN-7</v>
       </c>
-      <c r="Y7" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z7" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC7" s="64" t="s">
+      <c r="Y7" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD7" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>8</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="79" t="s">
         <v>187</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="79" t="s">
         <v>128</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I8" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L8" s="36" t="str">
+      <c r="G8" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="35" t="str">
         <f t="shared" ref="L8" si="22">CONCATENATE("", C8)</f>
         <v>Inteligente</v>
       </c>
-      <c r="M8" s="36" t="str">
+      <c r="M8" s="35" t="str">
         <f t="shared" si="11"/>
         <v>Agêntica.Natural</v>
       </c>
-      <c r="N8" s="36" t="str">
+      <c r="N8" s="35" t="str">
         <f t="shared" ref="N8" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E8),"."," ")," De "," de "))</f>
         <v>Humanos</v>
       </c>
-      <c r="O8" s="36" t="str">
+      <c r="O8" s="35" t="str">
         <f t="shared" si="13"/>
         <v>Calculista</v>
       </c>
-      <c r="P8" s="37" t="s">
+      <c r="P8" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="Q8" s="37" t="s">
+      <c r="Q8" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="R8" s="37" t="s">
+      <c r="R8" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="S8" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T8" s="37" t="str">
+      <c r="S8" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T8" s="36" t="str">
         <f t="shared" ref="T8" si="24">SUBSTITUTE(C8, ".", " ")</f>
         <v>Inteligente</v>
       </c>
-      <c r="U8" s="37" t="str">
+      <c r="U8" s="36" t="str">
         <f t="shared" si="15"/>
         <v>Agêntica Natural</v>
       </c>
-      <c r="V8" s="37" t="str">
+      <c r="V8" s="36" t="str">
         <f t="shared" si="16"/>
         <v>Humanos</v>
       </c>
-      <c r="W8" s="37" t="s">
+      <c r="W8" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X8" s="52" t="str">
+      <c r="X8" s="51" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-8</v>
       </c>
-      <c r="Y8" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z8" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA8" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB8" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC8" s="64" t="s">
+      <c r="Y8" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z8" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33">
         <v>9</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="79" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="81" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K9" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L9" s="36" t="str">
+      <c r="G9" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="35" t="str">
         <f t="shared" si="10"/>
         <v>Inteligente</v>
       </c>
-      <c r="M9" s="36" t="str">
+      <c r="M9" s="35" t="str">
         <f t="shared" si="10"/>
         <v>Agêntica.Artificial</v>
       </c>
-      <c r="N9" s="36" t="str">
+      <c r="N9" s="35" t="str">
         <f t="shared" si="12"/>
         <v>Artificiais</v>
       </c>
-      <c r="O9" s="36" t="str">
+      <c r="O9" s="35" t="str">
         <f t="shared" si="12"/>
         <v>Agente IA</v>
       </c>
-      <c r="P9" s="37" t="s">
+      <c r="P9" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="Q9" s="37" t="s">
+      <c r="Q9" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="R9" s="37" t="s">
+      <c r="R9" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="S9" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T9" s="37" t="str">
+      <c r="S9" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T9" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Inteligente</v>
       </c>
-      <c r="U9" s="37" t="str">
+      <c r="U9" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="V9" s="37" t="str">
+      <c r="V9" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Artificiais</v>
       </c>
-      <c r="W9" s="37" t="s">
+      <c r="W9" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X9" s="52" t="str">
+      <c r="X9" s="51" t="str">
         <f t="shared" si="4"/>
         <v>Key-AGEN-9</v>
       </c>
-      <c r="Y9" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z9" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB9" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC9" s="64" t="s">
+      <c r="Y9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC9" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD9" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>10</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D10" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="36" t="str">
+      <c r="G10" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="35" t="str">
         <f t="shared" si="10"/>
         <v>Inteligente</v>
       </c>
-      <c r="M10" s="36" t="str">
+      <c r="M10" s="35" t="str">
         <f t="shared" si="10"/>
         <v>Agêntica.Artificial</v>
       </c>
-      <c r="N10" s="36" t="str">
+      <c r="N10" s="35" t="str">
         <f t="shared" si="12"/>
         <v>Linguagens</v>
       </c>
-      <c r="O10" s="36" t="str">
+      <c r="O10" s="35" t="str">
         <f t="shared" si="12"/>
         <v>Idioma</v>
       </c>
-      <c r="P10" s="37" t="s">
+      <c r="P10" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="Q10" s="37" t="s">
+      <c r="Q10" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="R10" s="37" t="s">
+      <c r="R10" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="S10" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T10" s="37" t="str">
+      <c r="S10" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T10" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Inteligente</v>
       </c>
-      <c r="U10" s="37" t="str">
+      <c r="U10" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="V10" s="37" t="str">
+      <c r="V10" s="36" t="str">
         <f t="shared" si="14"/>
         <v>Linguagens</v>
       </c>
-      <c r="W10" s="37" t="s">
+      <c r="W10" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X10" s="52" t="str">
-        <f t="shared" ref="X10" si="25">CONCATENATE("Key-AGEN-",A10)</f>
+      <c r="X10" s="51" t="str">
+        <f t="shared" ref="X10:X18" si="25">CONCATENATE("Key-AGEN-",A10)</f>
         <v>Key-AGEN-10</v>
       </c>
-      <c r="Y10" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z10" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA10" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB10" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC10" s="64" t="s">
+      <c r="Y10" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>11</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="F11" s="35" t="s">
+      <c r="F11" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="36" t="str">
+      <c r="G11" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="35" t="str">
         <f t="shared" ref="L11:L12" si="26">CONCATENATE("", C11)</f>
         <v>Inteligente</v>
       </c>
-      <c r="M11" s="36" t="str">
+      <c r="M11" s="35" t="str">
         <f t="shared" ref="M11:M12" si="27">CONCATENATE("", D11)</f>
         <v>Agêntica.Artificial</v>
       </c>
-      <c r="N11" s="36" t="str">
+      <c r="N11" s="35" t="str">
         <f t="shared" ref="N11:N12" si="28">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Linguagens</v>
       </c>
-      <c r="O11" s="36" t="str">
+      <c r="O11" s="35" t="str">
         <f t="shared" ref="O11:O12" si="29">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F11),"."," ")," De "," de "))</f>
         <v>Linguagem</v>
       </c>
-      <c r="P11" s="37" t="s">
+      <c r="P11" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="Q11" s="37" t="s">
+      <c r="Q11" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="R11" s="37" t="s">
+      <c r="R11" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="S11" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T11" s="37" t="str">
+      <c r="S11" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T11" s="36" t="str">
         <f t="shared" ref="T11:T12" si="30">SUBSTITUTE(C11, ".", " ")</f>
         <v>Inteligente</v>
       </c>
-      <c r="U11" s="37" t="str">
+      <c r="U11" s="36" t="str">
         <f t="shared" ref="U11:U12" si="31">SUBSTITUTE(D11, ".", " ")</f>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="V11" s="37" t="str">
+      <c r="V11" s="36" t="str">
         <f t="shared" ref="V11:V12" si="32">SUBSTITUTE(E11, ".", " ")</f>
         <v>Linguagens</v>
       </c>
-      <c r="W11" s="37" t="s">
+      <c r="W11" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X11" s="52" t="str">
-        <f t="shared" si="4"/>
+      <c r="X11" s="51" t="str">
+        <f t="shared" si="25"/>
         <v>Key-AGEN-11</v>
       </c>
-      <c r="Y11" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z11" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA11" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB11" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC11" s="64" t="s">
+      <c r="Y11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33">
         <v>12</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K12" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L12" s="36" t="str">
+      <c r="G12" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L12" s="35" t="str">
         <f t="shared" si="26"/>
         <v>Inteligente</v>
       </c>
-      <c r="M12" s="36" t="str">
+      <c r="M12" s="35" t="str">
         <f t="shared" si="27"/>
         <v>Agêntica.Artificial</v>
       </c>
-      <c r="N12" s="36" t="str">
+      <c r="N12" s="35" t="str">
         <f t="shared" si="28"/>
         <v>Linguagens</v>
       </c>
-      <c r="O12" s="36" t="str">
+      <c r="O12" s="35" t="str">
         <f t="shared" si="29"/>
         <v>Sintaxe</v>
       </c>
-      <c r="P12" s="37" t="s">
+      <c r="P12" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="Q12" s="37" t="s">
+      <c r="Q12" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="R12" s="37" t="s">
+      <c r="R12" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="S12" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T12" s="37" t="str">
+      <c r="S12" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T12" s="36" t="str">
         <f t="shared" si="30"/>
         <v>Inteligente</v>
       </c>
-      <c r="U12" s="37" t="str">
+      <c r="U12" s="36" t="str">
         <f t="shared" si="31"/>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="V12" s="37" t="str">
+      <c r="V12" s="36" t="str">
         <f t="shared" si="32"/>
         <v>Linguagens</v>
       </c>
-      <c r="W12" s="37" t="s">
+      <c r="W12" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X12" s="52" t="str">
-        <f t="shared" si="4"/>
+      <c r="X12" s="51" t="str">
+        <f t="shared" si="25"/>
         <v>Key-AGEN-12</v>
       </c>
-      <c r="Y12" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z12" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA12" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB12" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="64" t="s">
+      <c r="Y12" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB12" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:30" s="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33">
         <v>13</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="B13" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="79" t="s">
         <v>174</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="F13" s="35" t="s">
+      <c r="F13" s="81" t="s">
         <v>177</v>
       </c>
-      <c r="G13" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K13" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L13" s="36" t="str">
+      <c r="G13" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="35" t="str">
         <f t="shared" ref="L13" si="33">CONCATENATE("", C13)</f>
         <v>Inteligente</v>
       </c>
-      <c r="M13" s="36" t="str">
+      <c r="M13" s="35" t="str">
         <f t="shared" ref="M13" si="34">CONCATENATE("", D13)</f>
         <v>Agêntica.Artificial</v>
       </c>
-      <c r="N13" s="36" t="str">
+      <c r="N13" s="35" t="str">
         <f t="shared" ref="N13" si="35">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
         <v>Linguagens</v>
       </c>
-      <c r="O13" s="36" t="str">
+      <c r="O13" s="35" t="str">
         <f t="shared" ref="O13" si="36">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F13),"."," ")," De "," de "))</f>
         <v>Semântico</v>
       </c>
-      <c r="P13" s="37" t="s">
+      <c r="P13" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="Q13" s="37" t="s">
+      <c r="Q13" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="R13" s="37" t="s">
+      <c r="R13" s="36" t="s">
         <v>206</v>
       </c>
-      <c r="S13" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T13" s="37" t="str">
-        <f t="shared" ref="T13:V14" si="37">SUBSTITUTE(C13, ".", " ")</f>
+      <c r="S13" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T13" s="36" t="str">
+        <f t="shared" ref="T13:V18" si="37">SUBSTITUTE(C13, ".", " ")</f>
         <v>Inteligente</v>
       </c>
-      <c r="U13" s="37" t="str">
+      <c r="U13" s="36" t="str">
         <f t="shared" ref="U13" si="38">SUBSTITUTE(D13, ".", " ")</f>
         <v>Agêntica Artificial</v>
       </c>
-      <c r="V13" s="37" t="str">
+      <c r="V13" s="36" t="str">
         <f t="shared" ref="V13" si="39">SUBSTITUTE(E13, ".", " ")</f>
         <v>Linguagens</v>
       </c>
-      <c r="W13" s="37" t="s">
+      <c r="W13" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X13" s="52" t="str">
-        <f t="shared" si="4"/>
+      <c r="X13" s="51" t="str">
+        <f t="shared" si="25"/>
         <v>Key-AGEN-13</v>
       </c>
-      <c r="Y13" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z13" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA13" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB13" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC13" s="64" t="s">
+      <c r="Y13" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB13" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD13" s="63" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="33">
         <v>14</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="C14" s="66" t="s">
+      <c r="C14" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="D14" s="66" t="s">
+      <c r="D14" s="80" t="s">
         <v>225</v>
       </c>
-      <c r="E14" s="66" t="s">
+      <c r="E14" s="80" t="s">
         <v>224</v>
       </c>
-      <c r="F14" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="G14" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="H14" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="I14" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="K14" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="36" t="str">
-        <f t="shared" ref="L14:O14" si="40">SUBSTITUTE(CONCATENATE("", C14), ".", " ")</f>
+      <c r="F14" s="80" t="s">
+        <v>249</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="35" t="str">
+        <f t="shared" ref="L14:O18" si="40">SUBSTITUTE(CONCATENATE("", C14), ".", " ")</f>
         <v>De API</v>
       </c>
-      <c r="M14" s="36" t="str">
+      <c r="M14" s="35" t="str">
         <f t="shared" si="40"/>
         <v>Macros</v>
       </c>
-      <c r="N14" s="36" t="str">
+      <c r="N14" s="35" t="str">
         <f t="shared" si="40"/>
         <v>Métodos</v>
       </c>
-      <c r="O14" s="36" t="str">
+      <c r="O14" s="35" t="str">
         <f t="shared" si="40"/>
-        <v>API Revit</v>
-      </c>
-      <c r="P14" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q14" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="R14" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="S14" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="T14" s="37" t="str">
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P14" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q14" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="R14" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="S14" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T14" s="36" t="str">
         <f t="shared" si="37"/>
         <v>De API</v>
       </c>
-      <c r="U14" s="37" t="str">
+      <c r="U14" s="36" t="str">
         <f t="shared" si="37"/>
         <v>Macros</v>
       </c>
-      <c r="V14" s="38" t="str">
+      <c r="V14" s="37" t="str">
         <f t="shared" si="37"/>
         <v>Métodos</v>
       </c>
-      <c r="W14" s="37" t="s">
+      <c r="W14" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="X14" s="52" t="str">
-        <f t="shared" si="4"/>
+      <c r="X14" s="51" t="str">
+        <f t="shared" si="25"/>
         <v>Key-AGEN-14</v>
       </c>
-      <c r="Y14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="64" t="s">
+      <c r="Y14" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z14" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="33">
+        <v>15</v>
+      </c>
+      <c r="B15" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" s="80" t="s">
+        <v>224</v>
+      </c>
+      <c r="F15" s="80" t="s">
+        <v>253</v>
+      </c>
+      <c r="G15" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="M15" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="N15" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O15" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P15" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q15" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="R15" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="S15" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T15" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>De API</v>
+      </c>
+      <c r="U15" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>Macros</v>
+      </c>
+      <c r="V15" s="37" t="str">
+        <f t="shared" si="37"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W15" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="X15" s="51" t="str">
+        <f t="shared" si="25"/>
+        <v>Key-AGEN-15</v>
+      </c>
+      <c r="Y15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="33">
+        <v>16</v>
+      </c>
+      <c r="B16" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="C16" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D16" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" s="80" t="s">
+        <v>224</v>
+      </c>
+      <c r="F16" s="80" t="s">
+        <v>257</v>
+      </c>
+      <c r="G16" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="M16" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="N16" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O16" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q16" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="R16" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="S16" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T16" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>De API</v>
+      </c>
+      <c r="U16" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>Macros</v>
+      </c>
+      <c r="V16" s="37" t="str">
+        <f t="shared" si="37"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W16" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="X16" s="51" t="str">
+        <f t="shared" si="25"/>
+        <v>Key-AGEN-16</v>
+      </c>
+      <c r="Y16" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z16" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA16" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB16" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC16" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD16" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="33">
+        <v>17</v>
+      </c>
+      <c r="B17" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D17" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="80" t="s">
+        <v>224</v>
+      </c>
+      <c r="F17" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="G17" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="M17" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="N17" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O17" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P17" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q17" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="R17" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="S17" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T17" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>De API</v>
+      </c>
+      <c r="U17" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>Macros</v>
+      </c>
+      <c r="V17" s="37" t="str">
+        <f t="shared" si="37"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W17" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="X17" s="51" t="str">
+        <f t="shared" si="25"/>
+        <v>Key-AGEN-17</v>
+      </c>
+      <c r="Y17" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z17" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA17" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB17" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC17" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD17" s="63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="64" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="33">
+        <v>18</v>
+      </c>
+      <c r="B18" s="79" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="80" t="s">
+        <v>223</v>
+      </c>
+      <c r="D18" s="80" t="s">
+        <v>225</v>
+      </c>
+      <c r="E18" s="80" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18" s="57" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="M18" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="N18" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O18" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P18" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q18" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="R18" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="S18" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="T18" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>De API</v>
+      </c>
+      <c r="U18" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v>Macros</v>
+      </c>
+      <c r="V18" s="37" t="str">
+        <f t="shared" si="37"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W18" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="X18" s="51" t="str">
+        <f t="shared" si="25"/>
+        <v>Key-AGEN-18</v>
+      </c>
+      <c r="Y18" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA18" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB18" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC18" s="63" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD18" s="63" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B14">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B18">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F13 F15:F1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+  <conditionalFormatting sqref="E18:F18">
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6 L3:O6 AD3:XFD6">
-    <cfRule type="cellIs" dxfId="15" priority="82" operator="equal">
+  <conditionalFormatting sqref="F1:F13 F19:F1048576">
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6 L3:O6 AE3:XFD6">
+    <cfRule type="cellIs" dxfId="15" priority="85" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="14" priority="637"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="672"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="673"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="682"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F13">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
+  <conditionalFormatting sqref="F14:F17">
     <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F1048576 F1:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="25"/>
+  <conditionalFormatting sqref="F19:F1048576 F1:F6">
+    <cfRule type="duplicateValues" dxfId="5" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R13">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3726,15 +4244,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="10" width="6" style="11" bestFit="1" customWidth="1"/>
     <col min="11" max="21" width="6" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="5" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>12</v>
       </c>
@@ -3799,7 +4317,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="5" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3874,16 +4392,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B299E44-CC41-4C47-93B0-FF411236635D}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.15234375" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" customWidth="1"/>
-    <col min="4" max="4" width="8.3046875" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3900,7 +4418,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="8.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25">
         <v>2</v>
       </c>
@@ -3931,54 +4449,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96F4F343-F8A9-4565-8E75-460BD2B52D7E}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AO15"/>
-  <sheetFormatPr defaultColWidth="4.84375" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="4.85546875" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" style="50" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.3828125" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.84375" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.84375" style="40" customWidth="1"/>
-    <col min="5" max="5" width="6.3828125" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5" style="40" customWidth="1"/>
-    <col min="7" max="7" width="5.84375" style="40" customWidth="1"/>
-    <col min="8" max="8" width="3.3828125" style="40" customWidth="1"/>
-    <col min="9" max="9" width="8.69140625" style="40" customWidth="1"/>
-    <col min="10" max="10" width="6.53515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="40" customWidth="1"/>
-    <col min="12" max="12" width="9.3828125" style="40" customWidth="1"/>
-    <col min="13" max="13" width="11.15234375" style="40" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.15234375" style="40" customWidth="1"/>
-    <col min="15" max="15" width="13.69140625" style="40" customWidth="1"/>
-    <col min="16" max="16" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.3828125" style="40" customWidth="1"/>
-    <col min="18" max="18" width="6.53515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4" style="40" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.69140625" style="40" customWidth="1"/>
-    <col min="22" max="22" width="6.15234375" style="40" customWidth="1"/>
-    <col min="23" max="23" width="8.53515625" style="40" customWidth="1"/>
-    <col min="24" max="24" width="6" style="40" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="48.3828125" style="40" customWidth="1"/>
-    <col min="26" max="26" width="7.3828125" style="54" customWidth="1"/>
-    <col min="27" max="27" width="39.69140625" style="54" customWidth="1"/>
-    <col min="28" max="28" width="5.69140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15" style="54" customWidth="1"/>
-    <col min="30" max="30" width="7.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.69140625" style="40" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="4.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="4.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="4.84375" style="40"/>
+    <col min="1" max="1" width="2.5703125" style="49" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" style="39" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5" style="39" customWidth="1"/>
+    <col min="7" max="7" width="5.85546875" style="39" customWidth="1"/>
+    <col min="8" max="8" width="3.42578125" style="39" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="39" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="39" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="39" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="39" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" style="39" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" style="39" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" style="39" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="39" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" style="39" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4" style="39" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.7109375" style="39" customWidth="1"/>
+    <col min="22" max="22" width="6.140625" style="39" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="39" customWidth="1"/>
+    <col min="24" max="24" width="6" style="39" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.42578125" style="39" customWidth="1"/>
+    <col min="26" max="26" width="7.42578125" style="53" customWidth="1"/>
+    <col min="27" max="27" width="39.7109375" style="53" customWidth="1"/>
+    <col min="28" max="28" width="5.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" style="53" customWidth="1"/>
+    <col min="30" max="30" width="7.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.7109375" style="39" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="4.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="4.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="4.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="4.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="4.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="4.28515625" style="39" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="4.7109375" style="39" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="4.85546875" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="20.7" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:41" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="22" t="s">
@@ -4049,69 +4567,69 @@
       <c r="Y1" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="Z1" s="61" t="s">
+      <c r="Z1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AA1" s="74" t="s">
+      <c r="AA1" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="AB1" s="61" t="s">
+      <c r="AB1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AC1" s="74" t="s">
+      <c r="AC1" s="72" t="s">
         <v>156</v>
       </c>
       <c r="AD1" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="AE1" s="79" t="s">
+      <c r="AE1" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="AF1" s="61" t="s">
+      <c r="AF1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AG1" s="60" t="s">
+      <c r="AG1" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="AH1" s="61" t="s">
+      <c r="AH1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AI1" s="60" t="s">
+      <c r="AI1" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="AJ1" s="61" t="s">
+      <c r="AJ1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AK1" s="60" t="s">
+      <c r="AK1" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="AL1" s="61" t="s">
+      <c r="AL1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AM1" s="60" t="s">
+      <c r="AM1" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="AN1" s="61" t="s">
+      <c r="AN1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="AO1" s="60" t="s">
+      <c r="AO1" s="59" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="49">
+    <row r="2" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="48">
         <v>2</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="80" t="s">
+      <c r="D2" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="29" t="s">
@@ -4174,75 +4692,75 @@
       <c r="Y2" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="Z2" s="62" t="s">
+      <c r="Z2" s="61" t="s">
         <v>157</v>
       </c>
-      <c r="AA2" s="75" t="s">
+      <c r="AA2" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="AB2" s="62" t="s">
+      <c r="AB2" s="61" t="s">
         <v>159</v>
       </c>
-      <c r="AC2" s="76" t="s">
+      <c r="AC2" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="AD2" s="63" t="s">
+      <c r="AD2" s="62" t="s">
         <v>161</v>
       </c>
       <c r="AE2" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="AF2" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG2" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH2" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI2" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ2" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK2" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL2" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM2" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN2" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO2" s="68" t="s">
+      <c r="AF2" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG2" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH2" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI2" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ2" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK2" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL2" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM2" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN2" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO2" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="49">
+    <row r="3" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="48">
         <v>3</v>
       </c>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="80" t="s">
+      <c r="E3" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H3" s="29" t="s">
@@ -4299,75 +4817,75 @@
       <c r="Y3" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="Z3" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA3" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB3" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC3" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD3" s="63" t="s">
+      <c r="Z3" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA3" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB3" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC3" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD3" s="62" t="s">
         <v>161</v>
       </c>
       <c r="AE3" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="AF3" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG3" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH3" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI3" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ3" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK3" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL3" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM3" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN3" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO3" s="68" t="s">
+      <c r="AF3" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL3" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN3" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="49">
+    <row r="4" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="48">
         <v>4</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="40" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="80" t="s">
+      <c r="E4" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F4" s="56" t="s">
+      <c r="F4" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G4" s="57" t="s">
+      <c r="G4" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H4" s="29" t="s">
@@ -4424,75 +4942,75 @@
       <c r="Y4" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="Z4" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA4" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB4" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC4" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD4" s="63" t="s">
+      <c r="Z4" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA4" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC4" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD4" s="62" t="s">
         <v>161</v>
       </c>
       <c r="AE4" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="AF4" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG4" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH4" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI4" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ4" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK4" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL4" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM4" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN4" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO4" s="68" t="s">
+      <c r="AF4" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG4" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH4" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ4" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK4" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL4" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM4" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN4" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="49">
+    <row r="5" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="48">
         <v>5</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="80" t="s">
+      <c r="E5" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G5" s="57" t="s">
+      <c r="G5" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H5" s="29" t="s">
@@ -4549,75 +5067,75 @@
       <c r="Y5" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="Z5" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA5" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB5" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC5" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD5" s="63" t="s">
+      <c r="Z5" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA5" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB5" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD5" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF5" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG5" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH5" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI5" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ5" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK5" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL5" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM5" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN5" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO5" s="68" t="s">
+      <c r="AF5" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG5" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH5" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI5" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ5" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK5" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL5" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM5" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN5" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO5" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="49">
+    <row r="6" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="48">
         <v>6</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F6" s="56" t="s">
+      <c r="F6" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H6" s="29" t="s">
@@ -4674,75 +5192,75 @@
       <c r="Y6" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="Z6" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA6" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB6" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC6" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD6" s="63" t="s">
+      <c r="Z6" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA6" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB6" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC6" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD6" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF6" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG6" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH6" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI6" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ6" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK6" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL6" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM6" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN6" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO6" s="68" t="s">
+      <c r="AF6" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG6" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH6" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI6" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ6" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK6" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL6" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM6" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN6" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO6" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="49">
+    <row r="7" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="48">
         <v>7</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="80" t="s">
+      <c r="E7" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F7" s="56" t="s">
+      <c r="F7" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G7" s="57" t="s">
+      <c r="G7" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H7" s="29" t="s">
@@ -4799,75 +5317,75 @@
       <c r="Y7" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="Z7" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB7" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC7" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD7" s="63" t="s">
+      <c r="Z7" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD7" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF7" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG7" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH7" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI7" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ7" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK7" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL7" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM7" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN7" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO7" s="68" t="s">
+      <c r="AF7" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG7" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH7" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI7" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ7" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK7" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL7" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM7" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN7" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO7" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="49">
+    <row r="8" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="48">
         <v>8</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="80" t="s">
+      <c r="E8" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H8" s="29" t="s">
@@ -4924,75 +5442,75 @@
       <c r="Y8" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="Z8" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA8" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB8" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC8" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD8" s="63" t="s">
+      <c r="Z8" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA8" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC8" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD8" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE8" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG8" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI8" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK8" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM8" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN8" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO8" s="68" t="s">
+      <c r="AF8" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG8" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH8" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI8" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ8" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK8" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL8" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM8" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN8" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO8" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="49">
+    <row r="9" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="48">
         <v>9</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="80" t="s">
+      <c r="E9" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F9" s="56" t="s">
+      <c r="F9" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G9" s="57" t="s">
+      <c r="G9" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H9" s="29" t="s">
@@ -5049,75 +5567,75 @@
       <c r="Y9" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="Z9" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA9" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB9" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC9" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD9" s="63" t="s">
+      <c r="Z9" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA9" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB9" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC9" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD9" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF9" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG9" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH9" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI9" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ9" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK9" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL9" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM9" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN9" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO9" s="68" t="s">
+      <c r="AF9" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG9" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH9" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI9" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ9" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK9" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL9" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM9" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN9" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO9" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="49">
-        <v>10</v>
-      </c>
-      <c r="B10" s="41" t="s">
+    <row r="10" spans="1:41" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="48">
+        <v>10</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="35" t="s">
+      <c r="C10" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="80" t="s">
+      <c r="E10" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="56" t="s">
+      <c r="F10" s="55" t="s">
         <v>144</v>
       </c>
-      <c r="G10" s="57" t="s">
+      <c r="G10" s="56" t="s">
         <v>145</v>
       </c>
       <c r="H10" s="29" t="s">
@@ -5174,195 +5692,195 @@
       <c r="Y10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="Z10" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA10" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB10" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC10" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD10" s="63" t="s">
+      <c r="Z10" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA10" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="61" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD10" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE10" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF10" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG10" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH10" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI10" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ10" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK10" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL10" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM10" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN10" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO10" s="68" t="s">
+      <c r="AF10" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG10" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH10" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI10" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ10" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK10" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL10" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM10" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN10" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO10" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49">
+    <row r="11" spans="1:41" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="48">
         <v>11</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="71" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="R11" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="S11" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="T11" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="U11" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="C11" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="L11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="O11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="R11" s="29" t="s">
-        <v>231</v>
-      </c>
-      <c r="S11" s="23" t="s">
-        <v>232</v>
-      </c>
-      <c r="T11" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="U11" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="V11" s="70" t="str">
+      <c r="V11" s="68" t="str">
         <f t="shared" ref="V11:V15" si="0">IF(W11="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="W11" s="71" t="s">
-        <v>236</v>
-      </c>
-      <c r="X11" s="69" t="s">
+      <c r="W11" s="69" t="s">
+        <v>232</v>
+      </c>
+      <c r="X11" s="67" t="s">
         <v>76</v>
       </c>
       <c r="Y11" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="Z11" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA11" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB11" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC11" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD11" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z11" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA11" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC11" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD11" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE11" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF11" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG11" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH11" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI11" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ11" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK11" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL11" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM11" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN11" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO11" s="68" t="s">
+      <c r="AF11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG11" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI11" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK11" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM11" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN11" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO11" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="49">
+    <row r="12" spans="1:41" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="48">
         <v>12</v>
       </c>
-      <c r="B12" s="73" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="80" t="s">
+      <c r="B12" s="71" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="29" t="s">
@@ -5402,93 +5920,93 @@
         <v>10</v>
       </c>
       <c r="R12" s="29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="T12" s="29" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="U12" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="V12" s="70" t="str">
+        <v>234</v>
+      </c>
+      <c r="V12" s="68" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="W12" s="71" t="s">
-        <v>240</v>
-      </c>
-      <c r="X12" s="69" t="s">
+      <c r="W12" s="69" t="s">
+        <v>236</v>
+      </c>
+      <c r="X12" s="67" t="s">
         <v>76</v>
       </c>
       <c r="Y12" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z12" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA12" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB12" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD12" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="Z12" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA12" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB12" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC12" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE12" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF12" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG12" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH12" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI12" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ12" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK12" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL12" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM12" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN12" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO12" s="68" t="s">
+      <c r="AF12" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG12" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH12" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI12" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ12" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK12" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL12" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM12" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN12" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO12" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49">
+    <row r="13" spans="1:41" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="48">
         <v>13</v>
       </c>
-      <c r="B13" s="73" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D13" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="80" t="s">
+      <c r="B13" s="71" t="s">
+        <v>237</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D13" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="29" t="s">
@@ -5528,93 +6046,93 @@
         <v>10</v>
       </c>
       <c r="R13" s="29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="T13" s="29" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="U13" s="23" t="s">
-        <v>242</v>
-      </c>
-      <c r="V13" s="70" t="str">
+        <v>238</v>
+      </c>
+      <c r="V13" s="68" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="W13" s="71" t="s">
-        <v>244</v>
-      </c>
-      <c r="X13" s="69" t="s">
+      <c r="W13" s="69" t="s">
+        <v>240</v>
+      </c>
+      <c r="X13" s="67" t="s">
         <v>76</v>
       </c>
       <c r="Y13" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="Z13" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA13" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB13" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC13" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD13" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="Z13" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA13" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB13" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC13" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD13" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE13" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF13" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG13" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH13" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI13" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ13" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK13" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL13" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM13" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN13" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO13" s="68" t="s">
+      <c r="AF13" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG13" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH13" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI13" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ13" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK13" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL13" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM13" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN13" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO13" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="49">
+    <row r="14" spans="1:41" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="48">
         <v>14</v>
       </c>
-      <c r="B14" s="73" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D14" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="80" t="s">
+      <c r="B14" s="71" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="29" t="s">
@@ -5654,93 +6172,93 @@
         <v>10</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="S14" s="23" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="T14" s="29" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="U14" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="V14" s="70" t="str">
+        <v>242</v>
+      </c>
+      <c r="V14" s="68" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="W14" s="71" t="s">
-        <v>248</v>
-      </c>
-      <c r="X14" s="69" t="s">
+      <c r="W14" s="69" t="s">
+        <v>244</v>
+      </c>
+      <c r="X14" s="67" t="s">
         <v>76</v>
       </c>
       <c r="Y14" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="Z14" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA14" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB14" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD14" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="Z14" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA14" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB14" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC14" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD14" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE14" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF14" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG14" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH14" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI14" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ14" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK14" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL14" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM14" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN14" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO14" s="68" t="s">
+      <c r="AF14" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG14" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH14" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI14" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK14" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL14" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM14" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN14" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO14" s="66" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="72" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="49">
+    <row r="15" spans="1:41" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="48">
         <v>15</v>
       </c>
-      <c r="B15" s="73" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="80" t="s">
+      <c r="B15" s="71" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="80" t="s">
+        <v>261</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="78" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="29" t="s">
@@ -5780,87 +6298,87 @@
         <v>10</v>
       </c>
       <c r="R15" s="29" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="S15" s="23" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="T15" s="29" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="U15" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="V15" s="70" t="str">
+        <v>246</v>
+      </c>
+      <c r="V15" s="68" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="W15" s="71" t="s">
-        <v>252</v>
-      </c>
-      <c r="X15" s="69" t="s">
+      <c r="W15" s="69" t="s">
+        <v>248</v>
+      </c>
+      <c r="X15" s="67" t="s">
         <v>76</v>
       </c>
       <c r="Y15" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="Z15" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA15" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AB15" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC15" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD15" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z15" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA15" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB15" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC15" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD15" s="62" t="s">
         <v>10</v>
       </c>
       <c r="AE15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AF15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AG15" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AH15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI15" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AJ15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AK15" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AM15" s="68" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN15" s="67" t="s">
-        <v>10</v>
-      </c>
-      <c r="AO15" s="68" t="s">
+      <c r="AF15" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG15" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH15" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI15" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ15" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK15" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL15" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM15" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN15" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO15" s="66" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B11:B15">
-    <cfRule type="duplicateValues" dxfId="2" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AO15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Agentes.xlsx
+++ b/Versão5/PRO/Ontologia_Agentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41107FD7-E353-4818-8275-975C914134DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F02714-6289-4C22-9D3D-0FC57D7FA37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="330">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -247,28 +247,7 @@
     <t>Escola Politécnica da UFRJ</t>
   </si>
   <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>Observações</t>
@@ -926,13 +905,172 @@
   </si>
   <si>
     <t>Operativa.Gramatical</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1015,8 +1153,16 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1167,6 +1313,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -1264,10 +1416,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1489,8 +1642,36 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="27">
@@ -2156,16 +2337,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="52" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="51.7109375" style="52" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="45" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.28515625" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>45</v>
       </c>
@@ -2173,10 +2354,10 @@
         <v>46</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>47</v>
       </c>
@@ -2184,21 +2365,21 @@
         <v>48</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>49</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>50</v>
       </c>
@@ -2206,10 +2387,10 @@
         <v>33</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>51</v>
       </c>
@@ -2218,10 +2399,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
         <v>52</v>
       </c>
@@ -2230,10 +2411,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>53</v>
       </c>
@@ -2241,21 +2422,21 @@
         <v>54</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="77" t="s">
         <v>55</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>56</v>
       </c>
@@ -2263,202 +2444,464 @@
         <v>57</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="B17" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
         <v>60</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C12" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>67</v>
       </c>
       <c r="B18" s="20">
         <f ca="1">NOW()</f>
-        <v>46274.512839236108</v>
+        <v>46276.434401967592</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>88</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="77" t="s">
+        <v>81</v>
       </c>
       <c r="B20" s="20" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>89</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="77" t="s">
+        <v>82</v>
       </c>
       <c r="B21" s="20" t="str">
         <f>_xlfn.TRANSLATE(B19,"pt","es")</f>
         <v>Traducciones al español e inglés incorporadas. Las traducciones deben revisarse constantemente</v>
       </c>
       <c r="C21" s="44" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>93</v>
-      </c>
       <c r="C24" s="44" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B25" s="21" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formaliza las clases para agentes.</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>82</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="77" t="s">
+        <v>75</v>
       </c>
       <c r="B26" s="21" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize agent classes.</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>86</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="77" t="s">
+        <v>284</v>
+      </c>
+      <c r="B27" s="78" t="s">
+        <v>307</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="77" t="s">
+        <v>285</v>
+      </c>
+      <c r="B28" s="79" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="77" t="s">
+        <v>286</v>
+      </c>
+      <c r="B29" s="79" t="s">
+        <v>309</v>
+      </c>
+      <c r="C29" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="77" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" s="80" t="s">
+        <v>310</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>288</v>
+      </c>
+      <c r="B31" s="81" t="s">
+        <v>311</v>
+      </c>
+      <c r="C31" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="77" t="s">
+        <v>289</v>
+      </c>
+      <c r="B32" s="81" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="77" t="s">
+        <v>290</v>
+      </c>
+      <c r="B33" s="81" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="77" t="s">
+        <v>291</v>
+      </c>
+      <c r="B34" s="82" t="s">
+        <v>314</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="77" t="s">
+        <v>292</v>
+      </c>
+      <c r="B35" s="82" t="s">
+        <v>315</v>
+      </c>
+      <c r="C35" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="77" t="s">
+        <v>293</v>
+      </c>
+      <c r="B36" s="81" t="s">
+        <v>316</v>
+      </c>
+      <c r="C36" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="77" t="s">
+        <v>294</v>
+      </c>
+      <c r="B37" s="82" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="77" t="s">
+        <v>295</v>
+      </c>
+      <c r="B38" s="81" t="s">
+        <v>318</v>
+      </c>
+      <c r="C38" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="77" t="s">
+        <v>296</v>
+      </c>
+      <c r="B39" s="83" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="77" t="s">
+        <v>297</v>
+      </c>
+      <c r="B40" s="83" t="s">
+        <v>320</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="B41" s="84" t="s">
+        <v>321</v>
+      </c>
+      <c r="C41" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="77" t="s">
+        <v>299</v>
+      </c>
+      <c r="B42" s="85" t="s">
+        <v>322</v>
+      </c>
+      <c r="C42" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="77" t="s">
+        <v>300</v>
+      </c>
+      <c r="B43" s="85" t="s">
+        <v>323</v>
+      </c>
+      <c r="C43" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="77" t="s">
+        <v>301</v>
+      </c>
+      <c r="B44" s="85" t="s">
+        <v>324</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="77" t="s">
+        <v>302</v>
+      </c>
+      <c r="B45" s="85" t="s">
+        <v>325</v>
+      </c>
+      <c r="C45" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="77" t="s">
+        <v>303</v>
+      </c>
+      <c r="B46" s="85" t="s">
+        <v>326</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="77" t="s">
+        <v>304</v>
+      </c>
+      <c r="B47" s="85" t="s">
+        <v>327</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="77" t="s">
+        <v>305</v>
+      </c>
+      <c r="B48" s="85" t="s">
+        <v>328</v>
+      </c>
+      <c r="C48" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="77" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" s="85" t="s">
+        <v>329</v>
+      </c>
+      <c r="C49" s="44" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{283F9496-37BC-49D7-A800-DC59E828CC50}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{29A161D6-1EB9-4F10-9B14-ED537677EDB1}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{2D5335AC-98ED-4F78-AC2B-9885AEC5F58D}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{197EC2DF-45AD-43AF-BD4D-12E872FF1838}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{BBC1E330-4B52-422C-97DA-7951940336A0}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{25A3B404-6193-496B-883C-D262AEAD2E36}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{1C56988C-14F9-4EE2-BE3A-A916DBCCE567}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -2548,10 +2991,10 @@
         <v>44</v>
       </c>
       <c r="R1" s="42" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="S1" s="76" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="T1" s="16" t="s">
         <v>34</v>
@@ -2569,22 +3012,22 @@
         <v>9</v>
       </c>
       <c r="Y1" s="30" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Z1" s="30" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AA1" s="30" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="AB1" s="30" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="AC1" s="30" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AD1" s="30" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:30" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2592,19 +3035,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="74" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C2" s="74" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D2" s="74" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E2" s="74" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F2" s="34" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G2" s="53" t="s">
         <v>10</v>
@@ -2638,13 +3081,13 @@
         <v>Agente Humano</v>
       </c>
       <c r="P2" s="36" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="Q2" s="36" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="R2" s="36" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="S2" s="72" t="s">
         <v>10</v>
@@ -2662,7 +3105,7 @@
         <v>Orquestra Humana</v>
       </c>
       <c r="W2" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X2" s="50" t="str">
         <f t="shared" ref="X2:X21" si="4">CONCATENATE("Key-AGEN-",A2)</f>
@@ -2692,19 +3135,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="74" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D3" s="74" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E3" s="74" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F3" s="34" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G3" s="53" t="s">
         <v>10</v>
@@ -2738,13 +3181,13 @@
         <v>Agente Artificial</v>
       </c>
       <c r="P3" s="36" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="36" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="R3" s="36" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="S3" s="72" t="s">
         <v>10</v>
@@ -2762,7 +3205,7 @@
         <v>Orquestra Artificial</v>
       </c>
       <c r="W3" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X3" s="50" t="str">
         <f t="shared" si="4"/>
@@ -2792,19 +3235,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="74" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D4" s="74" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E4" s="74" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F4" s="34" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G4" s="53" t="s">
         <v>10</v>
@@ -2838,13 +3281,13 @@
         <v>Gherkin</v>
       </c>
       <c r="P4" s="36" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="R4" s="36" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="S4" s="72" t="s">
         <v>10</v>
@@ -2862,7 +3305,7 @@
         <v>Instrumento Computacional</v>
       </c>
       <c r="W4" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X4" s="50" t="str">
         <f t="shared" si="4"/>
@@ -2892,19 +3335,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="74" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D5" s="74" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E5" s="74" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G5" s="53" t="s">
         <v>10</v>
@@ -2938,13 +3381,13 @@
         <v>Sintático</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="R5" s="36" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="S5" s="72" t="s">
         <v>10</v>
@@ -2962,7 +3405,7 @@
         <v>Instrumento Computacional</v>
       </c>
       <c r="W5" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X5" s="50" t="str">
         <f t="shared" si="4"/>
@@ -2992,19 +3435,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="74" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C6" s="74" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D6" s="74" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E6" s="74" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="G6" s="53" t="s">
         <v>10</v>
@@ -3038,13 +3481,13 @@
         <v>Semântico</v>
       </c>
       <c r="P6" s="36" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="Q6" s="36" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="R6" s="36" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="S6" s="72" t="s">
         <v>10</v>
@@ -3062,7 +3505,7 @@
         <v>Instrumento Computacional</v>
       </c>
       <c r="W6" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X6" s="50" t="str">
         <f t="shared" ref="X6" si="10">CONCATENATE("Key-AGEN-",A6)</f>
@@ -3092,19 +3535,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="74" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D7" s="74" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E7" s="74" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="G7" s="53" t="s">
         <v>10</v>
@@ -3138,13 +3581,13 @@
         <v>Gramático</v>
       </c>
       <c r="P7" s="36" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="Q7" s="36" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="R7" s="36" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="S7" s="72" t="s">
         <v>10</v>
@@ -3162,7 +3605,7 @@
         <v>Instrumento Computacional</v>
       </c>
       <c r="W7" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X7" s="50" t="str">
         <f t="shared" si="4"/>
@@ -3192,19 +3635,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C8" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D8" s="74" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E8" s="74" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G8" s="53" t="s">
         <v>10</v>
@@ -3238,13 +3681,13 @@
         <v>Projetista</v>
       </c>
       <c r="P8" s="36" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="Q8" s="36" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="R8" s="36" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="S8" s="72" t="s">
         <v>10</v>
@@ -3262,7 +3705,7 @@
         <v>Inteligência Humana</v>
       </c>
       <c r="W8" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X8" s="50" t="str">
         <f t="shared" si="4"/>
@@ -3292,19 +3735,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C9" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D9" s="74" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E9" s="74" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F9" s="34" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="G9" s="53" t="s">
         <v>10</v>
@@ -3338,13 +3781,13 @@
         <v>Calculista</v>
       </c>
       <c r="P9" s="36" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="Q9" s="36" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="R9" s="36" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="S9" s="72" t="s">
         <v>10</v>
@@ -3362,7 +3805,7 @@
         <v>Inteligência Humana</v>
       </c>
       <c r="W9" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X9" s="50" t="str">
         <f t="shared" ref="X9:X10" si="20">CONCATENATE("Key-AGEN-",A9)</f>
@@ -3392,19 +3835,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C10" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D10" s="74" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E10" s="74" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G10" s="53" t="s">
         <v>10</v>
@@ -3438,13 +3881,13 @@
         <v>Consultoria</v>
       </c>
       <c r="P10" s="36" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="Q10" s="36" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="R10" s="36" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="S10" s="72" t="s">
         <v>10</v>
@@ -3462,7 +3905,7 @@
         <v>Inteligência Humana</v>
       </c>
       <c r="W10" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X10" s="50" t="str">
         <f t="shared" si="20"/>
@@ -3492,19 +3935,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C11" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D11" s="74" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E11" s="74" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="F11" s="34" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G11" s="53" t="s">
         <v>10</v>
@@ -3538,13 +3981,13 @@
         <v>Idioma</v>
       </c>
       <c r="P11" s="36" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="Q11" s="36" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="R11" s="36" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="S11" s="72" t="s">
         <v>10</v>
@@ -3562,7 +4005,7 @@
         <v>Inteligência Humana</v>
       </c>
       <c r="W11" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X11" s="50" t="str">
         <f t="shared" si="4"/>
@@ -3592,19 +4035,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C12" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D12" s="74" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E12" s="74" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G12" s="53" t="s">
         <v>10</v>
@@ -3638,13 +4081,13 @@
         <v>Agente de IA</v>
       </c>
       <c r="P12" s="36" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="Q12" s="36" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="R12" s="36" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="S12" s="72" t="s">
         <v>10</v>
@@ -3662,7 +4105,7 @@
         <v>Agêntica Artificial</v>
       </c>
       <c r="W12" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X12" s="50" t="str">
         <f t="shared" si="4"/>
@@ -3692,19 +4135,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C13" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D13" s="74" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E13" s="74" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="G13" s="53" t="s">
         <v>10</v>
@@ -3738,13 +4181,13 @@
         <v>Linguagem Computacional</v>
       </c>
       <c r="P13" s="36" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="Q13" s="36" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R13" s="36" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="S13" s="72" t="s">
         <v>10</v>
@@ -3762,7 +4205,7 @@
         <v>Agêntica Artificial</v>
       </c>
       <c r="W13" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X13" s="50" t="str">
         <f t="shared" si="4"/>
@@ -3792,19 +4235,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C14" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D14" s="74" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E14" s="74" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="G14" s="53" t="s">
         <v>10</v>
@@ -3838,13 +4281,13 @@
         <v>Operativa Sintática</v>
       </c>
       <c r="P14" s="36" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="Q14" s="36" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="R14" s="36" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="S14" s="72" t="s">
         <v>10</v>
@@ -3862,7 +4305,7 @@
         <v>Agêntica Artificial</v>
       </c>
       <c r="W14" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X14" s="50" t="str">
         <f t="shared" si="4"/>
@@ -3892,19 +4335,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C15" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D15" s="74" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E15" s="74" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G15" s="53" t="s">
         <v>10</v>
@@ -3938,13 +4381,13 @@
         <v>Operativa Semântica</v>
       </c>
       <c r="P15" s="36" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R15" s="36" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="S15" s="72" t="s">
         <v>10</v>
@@ -3962,7 +4405,7 @@
         <v>Agêntica Artificial</v>
       </c>
       <c r="W15" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X15" s="50" t="str">
         <f t="shared" ref="X15" si="34">CONCATENATE("Key-AGEN-",A15)</f>
@@ -3992,19 +4435,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="74" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C16" s="74" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D16" s="74" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E16" s="74" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="G16" s="53" t="s">
         <v>10</v>
@@ -4038,13 +4481,13 @@
         <v>Operativa Gramatical</v>
       </c>
       <c r="P16" s="36" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="Q16" s="36" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="R16" s="36" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="S16" s="72" t="s">
         <v>10</v>
@@ -4062,7 +4505,7 @@
         <v>Agêntica Artificial</v>
       </c>
       <c r="W16" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X16" s="50" t="str">
         <f t="shared" si="4"/>
@@ -4092,19 +4535,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="74" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C17" s="75" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D17" s="75" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E17" s="75" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F17" s="75" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="G17" s="53" t="s">
         <v>10</v>
@@ -4138,13 +4581,13 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P17" s="36" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="Q17" s="36" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="R17" s="36" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="S17" s="72" t="s">
         <v>10</v>
@@ -4162,7 +4605,7 @@
         <v>API Método</v>
       </c>
       <c r="W17" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X17" s="50" t="str">
         <f t="shared" si="4"/>
@@ -4192,19 +4635,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="74" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C18" s="75" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D18" s="75" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E18" s="75" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F18" s="75" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="G18" s="53" t="s">
         <v>10</v>
@@ -4238,13 +4681,13 @@
         <v>Função Global</v>
       </c>
       <c r="P18" s="36" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="Q18" s="36" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="R18" s="36" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="S18" s="72" t="s">
         <v>10</v>
@@ -4262,7 +4705,7 @@
         <v>API Método</v>
       </c>
       <c r="W18" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X18" s="50" t="str">
         <f t="shared" si="4"/>
@@ -4292,19 +4735,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="74" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C19" s="75" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D19" s="75" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E19" s="75" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F19" s="75" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="G19" s="53" t="s">
         <v>10</v>
@@ -4338,13 +4781,13 @@
         <v>Função Local</v>
       </c>
       <c r="P19" s="36" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="Q19" s="36" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="R19" s="36" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="S19" s="72" t="s">
         <v>10</v>
@@ -4362,7 +4805,7 @@
         <v>API Método</v>
       </c>
       <c r="W19" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X19" s="50" t="str">
         <f t="shared" si="4"/>
@@ -4392,19 +4835,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="74" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C20" s="75" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D20" s="75" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E20" s="75" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F20" s="75" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="G20" s="53" t="s">
         <v>10</v>
@@ -4438,13 +4881,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P20" s="36" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Q20" s="36" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="R20" s="36" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="S20" s="72" t="s">
         <v>10</v>
@@ -4462,7 +4905,7 @@
         <v>API Método</v>
       </c>
       <c r="W20" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X20" s="50" t="str">
         <f t="shared" si="4"/>
@@ -4492,19 +4935,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="74" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C21" s="75" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D21" s="75" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E21" s="75" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F21" s="75" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="G21" s="53" t="s">
         <v>10</v>
@@ -4538,13 +4981,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P21" s="36" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Q21" s="36" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="R21" s="36" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="S21" s="72" t="s">
         <v>10</v>
@@ -4562,7 +5005,7 @@
         <v>API Método Visual</v>
       </c>
       <c r="W21" s="36" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="X21" s="50" t="str">
         <f t="shared" si="4"/>
@@ -4807,16 +5250,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25">
@@ -4891,94 +5334,94 @@
         <v>11</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H1" s="24" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="M1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Q1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="R1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="S1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="T1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="U1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="V1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="W1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="X1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Y1" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Z1" s="55" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AA1" s="65" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AB1" s="55" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AC1" s="65" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AD1" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="AE1" s="70" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -4986,10 +5429,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D2" s="38" t="s">
         <v>10</v>
@@ -5004,76 +5447,76 @@
         <v>10</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I2" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K2" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="M2" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q2" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="T2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="U2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="V2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="X2" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y2" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z2" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="J2" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K2" s="23" t="s">
+      <c r="AA2" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="L2" s="29" t="s">
+      <c r="AB2" s="56" t="s">
+        <v>144</v>
+      </c>
+      <c r="AC2" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="AD2" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="P2" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q2" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="T2" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="U2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="V2" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="W2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="X2" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y2" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z2" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA2" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="AB2" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="AC2" s="67" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD2" s="57" t="s">
-        <v>153</v>
-      </c>
       <c r="AE2" s="23" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5081,16 +5524,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E3" s="71" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>10</v>
@@ -5099,10 +5542,10 @@
         <v>10</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="J3" s="29" t="s">
         <v>10</v>
@@ -5147,10 +5590,10 @@
         <v>10</v>
       </c>
       <c r="X3" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y3" s="23" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="Z3" s="56" t="s">
         <v>10</v>
@@ -5165,10 +5608,10 @@
         <v>10</v>
       </c>
       <c r="AD3" s="57" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AE3" s="23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5176,16 +5619,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>10</v>
@@ -5194,10 +5637,10 @@
         <v>10</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J4" s="29" t="s">
         <v>10</v>
@@ -5242,10 +5685,10 @@
         <v>10</v>
       </c>
       <c r="X4" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y4" s="23" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="Z4" s="56" t="s">
         <v>10</v>
@@ -5260,10 +5703,10 @@
         <v>10</v>
       </c>
       <c r="AD4" s="57" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AE4" s="23" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -5271,53 +5714,53 @@
         <v>5</v>
       </c>
       <c r="B5" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="D5" s="38" t="s">
+      <c r="E5" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K5" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="M5" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="N5" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="O5" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E5" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G5" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K5" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="M5" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="N5" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="P5" s="29" t="s">
+      <c r="Q5" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="Q5" s="23" t="s">
-        <v>116</v>
-      </c>
       <c r="R5" s="29" t="s">
         <v>10</v>
       </c>
@@ -5337,10 +5780,10 @@
         <v>10</v>
       </c>
       <c r="X5" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="23" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="Z5" s="56" t="s">
         <v>10</v>
@@ -5366,53 +5809,53 @@
         <v>6</v>
       </c>
       <c r="B6" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G6" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="D6" s="38" t="s">
+      <c r="J6" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K6" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="M6" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="O6" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="P6" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E6" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G6" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H6" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="L6" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="M6" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="N6" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O6" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="P6" s="29" t="s">
+      <c r="Q6" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="Q6" s="23" t="s">
-        <v>116</v>
-      </c>
       <c r="R6" s="29" t="s">
         <v>10</v>
       </c>
@@ -5432,10 +5875,10 @@
         <v>10</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y6" s="23" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="Z6" s="56" t="s">
         <v>10</v>
@@ -5461,53 +5904,53 @@
         <v>7</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D7" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G7" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="N7" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="O7" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="P7" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F7" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G7" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H7" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="L7" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="M7" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="N7" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O7" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="P7" s="29" t="s">
+      <c r="Q7" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="Q7" s="23" t="s">
-        <v>116</v>
-      </c>
       <c r="R7" s="29" t="s">
         <v>10</v>
       </c>
@@ -5527,10 +5970,10 @@
         <v>10</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="23" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="Z7" s="56" t="s">
         <v>10</v>
@@ -5556,52 +5999,52 @@
         <v>8</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C8" s="34" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D8" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="O8" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P8" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G8" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O8" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="P8" s="29" t="s">
-        <v>109</v>
-      </c>
       <c r="Q8" s="23" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="R8" s="29" t="s">
         <v>10</v>
@@ -5622,10 +6065,10 @@
         <v>10</v>
       </c>
       <c r="X8" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y8" s="23" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="Z8" s="56" t="s">
         <v>10</v>
@@ -5651,52 +6094,52 @@
         <v>9</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C9" s="34" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="D9" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="N9" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="O9" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="P9" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E9" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G9" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="N9" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O9" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>109</v>
-      </c>
       <c r="Q9" s="23" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="R9" s="29" t="s">
         <v>10</v>
@@ -5717,10 +6160,10 @@
         <v>10</v>
       </c>
       <c r="X9" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y9" s="23" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="Z9" s="56" t="s">
         <v>10</v>
@@ -5746,52 +6189,52 @@
         <v>10</v>
       </c>
       <c r="B10" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="34" t="s">
-        <v>250</v>
-      </c>
-      <c r="D10" s="38" t="s">
+      <c r="F10" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G10" s="71" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="L10" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="O10" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="P10" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="E10" s="71" t="s">
-        <v>141</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>247</v>
-      </c>
-      <c r="G10" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="N10" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="O10" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="P10" s="29" t="s">
-        <v>109</v>
-      </c>
       <c r="Q10" s="23" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="R10" s="29" t="s">
         <v>10</v>
@@ -5812,10 +6255,10 @@
         <v>10</v>
       </c>
       <c r="X10" s="29" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y10" s="23" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="Z10" s="56" t="s">
         <v>10</v>
@@ -5841,10 +6284,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C11" s="75" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D11" s="59" t="s">
         <v>10</v>
@@ -5889,29 +6332,29 @@
         <v>10</v>
       </c>
       <c r="R11" s="29" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="T11" s="29" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="U11" s="23" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="V11" s="61" t="str">
         <f t="shared" ref="V11:V15" si="0">IF(W11="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
       <c r="W11" s="62" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="X11" s="60" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y11" s="23" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="Z11" s="69" t="s">
         <v>10</v>
@@ -5937,10 +6380,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C12" s="75" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D12" s="59" t="s">
         <v>10</v>
@@ -5985,29 +6428,29 @@
         <v>10</v>
       </c>
       <c r="R12" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="S12" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="T12" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="U12" s="23" t="s">
         <v>197</v>
-      </c>
-      <c r="S12" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="T12" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="U12" s="23" t="s">
-        <v>204</v>
       </c>
       <c r="V12" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="W12" s="62" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="X12" s="60" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y12" s="23" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="Z12" s="69" t="s">
         <v>10</v>
@@ -6033,10 +6476,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C13" s="75" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D13" s="59" t="s">
         <v>10</v>
@@ -6081,29 +6524,29 @@
         <v>10</v>
       </c>
       <c r="R13" s="29" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="T13" s="29" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="U13" s="23" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="V13" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="W13" s="62" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="X13" s="60" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y13" s="23" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="Z13" s="69" t="s">
         <v>10</v>
@@ -6129,10 +6572,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C14" s="75" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D14" s="59" t="s">
         <v>10</v>
@@ -6177,29 +6620,29 @@
         <v>10</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="S14" s="23" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="T14" s="29" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="U14" s="23" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="V14" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="W14" s="62" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="X14" s="60" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y14" s="23" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="Z14" s="69" t="s">
         <v>10</v>
@@ -6225,10 +6668,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C15" s="75" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D15" s="59" t="s">
         <v>10</v>
@@ -6273,29 +6716,29 @@
         <v>10</v>
       </c>
       <c r="R15" s="29" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="S15" s="23" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="T15" s="29" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="U15" s="23" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="V15" s="61" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
       <c r="W15" s="62" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="X15" s="60" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="Y15" s="23" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="Z15" s="69" t="s">
         <v>10</v>
